--- a/research/traditional_assets/database/data/poland/poland_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_hospitals_healthcare_facilities.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07664150003345188</v>
+        <v>0.07653233118338834</v>
       </c>
       <c r="C2">
-        <v>211.1846790172967</v>
+        <v>209.8380753420732</v>
       </c>
       <c r="D2">
-        <v>203.6446790172967</v>
+        <v>204.3680753420732</v>
       </c>
       <c r="E2">
-        <v>-68.8</v>
+        <v>-66.73</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="G2">
         <v>7.54</v>
@@ -1439,28 +1439,28 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.104121</v>
       </c>
       <c r="N2">
-        <v>5.243333333333334</v>
+        <v>5.139212333333334</v>
       </c>
       <c r="O2">
-        <v>0.9962333333333335</v>
+        <v>0.9764503433333335</v>
       </c>
       <c r="P2">
-        <v>4.247100000000001</v>
+        <v>4.162761990000001</v>
       </c>
       <c r="Q2">
-        <v>6.0871</v>
+        <v>6.002761990000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07664150003345188</v>
+        <v>0.07689383957918014</v>
       </c>
       <c r="T2">
-        <v>0.5648729042001043</v>
+        <v>0.5694945915981052</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>50.35807698094846</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07653233118338834</v>
+        <v>0.07642316233332477</v>
       </c>
       <c r="C3">
-        <v>209.8380753420732</v>
+        <v>208.4966293539664</v>
       </c>
       <c r="D3">
-        <v>204.3680753420732</v>
+        <v>205.0966293539664</v>
       </c>
       <c r="E3">
-        <v>-66.73</v>
+        <v>-64.66</v>
       </c>
       <c r="F3">
-        <v>2.07</v>
+        <v>4.14</v>
       </c>
       <c r="G3">
         <v>7.54</v>
@@ -1521,28 +1521,28 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M3">
-        <v>0.104121</v>
+        <v>0.208242</v>
       </c>
       <c r="N3">
-        <v>5.139212333333334</v>
+        <v>5.035091333333334</v>
       </c>
       <c r="O3">
-        <v>0.9764503433333335</v>
+        <v>0.9566673533333334</v>
       </c>
       <c r="P3">
-        <v>4.162761990000001</v>
+        <v>4.07842398</v>
       </c>
       <c r="Q3">
-        <v>6.002761990000001</v>
+        <v>5.91842398</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07689383957918014</v>
+        <v>0.07715132891155589</v>
       </c>
       <c r="T3">
-        <v>0.5694945915981052</v>
+        <v>0.5742105991470856</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>50.35807698094846</v>
+        <v>25.17903849047423</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07642316233332477</v>
+        <v>0.07631399348326122</v>
       </c>
       <c r="C4">
-        <v>208.4966293539664</v>
+        <v>207.1603964104077</v>
       </c>
       <c r="D4">
-        <v>205.0966293539664</v>
+        <v>205.8303964104077</v>
       </c>
       <c r="E4">
-        <v>-64.66</v>
+        <v>-62.59</v>
       </c>
       <c r="F4">
-        <v>4.14</v>
+        <v>6.21</v>
       </c>
       <c r="G4">
         <v>7.54</v>
@@ -1603,28 +1603,28 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M4">
-        <v>0.208242</v>
+        <v>0.312363</v>
       </c>
       <c r="N4">
-        <v>5.035091333333334</v>
+        <v>4.930970333333334</v>
       </c>
       <c r="O4">
-        <v>0.9566673533333334</v>
+        <v>0.9368843633333334</v>
       </c>
       <c r="P4">
-        <v>4.07842398</v>
+        <v>3.99408597</v>
       </c>
       <c r="Q4">
-        <v>5.91842398</v>
+        <v>5.83408597</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07715132891155589</v>
+        <v>0.07741412730233116</v>
       </c>
       <c r="T4">
-        <v>0.5742105991470856</v>
+        <v>0.5790238439651173</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>25.17903849047423</v>
+        <v>16.78602566031615</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07631399348326122</v>
+        <v>0.07625342463319765</v>
       </c>
       <c r="C5">
-        <v>207.1603964104077</v>
+        <v>205.4997727143495</v>
       </c>
       <c r="D5">
-        <v>205.8303964104077</v>
+        <v>206.2397727143495</v>
       </c>
       <c r="E5">
-        <v>-62.59</v>
+        <v>-60.52</v>
       </c>
       <c r="F5">
-        <v>6.21</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G5">
         <v>7.54</v>
@@ -1685,45 +1685,45 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M5">
-        <v>0.312363</v>
+        <v>0.428904</v>
       </c>
       <c r="N5">
-        <v>4.930970333333334</v>
+        <v>4.814429333333334</v>
       </c>
       <c r="O5">
-        <v>0.9368843633333334</v>
+        <v>0.9147415733333335</v>
       </c>
       <c r="P5">
-        <v>3.99408597</v>
+        <v>3.89968776</v>
       </c>
       <c r="Q5">
-        <v>5.83408597</v>
+        <v>5.739687760000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07741412730233116</v>
+        <v>0.07768240065958089</v>
       </c>
       <c r="T5">
-        <v>0.5790238439651173</v>
+        <v>0.5839373647168578</v>
       </c>
       <c r="U5">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V5">
         <v>0.19</v>
       </c>
       <c r="W5">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y5">
-        <v>16.78602566031615</v>
+        <v>12.22495787713179</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07625342463319765</v>
+        <v>0.07622525578313409</v>
       </c>
       <c r="C6">
-        <v>205.4997727143495</v>
+        <v>203.6207172794878</v>
       </c>
       <c r="D6">
-        <v>206.2397727143495</v>
+        <v>206.4307172794878</v>
       </c>
       <c r="E6">
-        <v>-60.52</v>
+        <v>-58.45</v>
       </c>
       <c r="F6">
-        <v>8.279999999999999</v>
+        <v>10.35</v>
       </c>
       <c r="G6">
         <v>7.54</v>
@@ -1767,45 +1767,45 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M6">
-        <v>0.428904</v>
+        <v>0.553725</v>
       </c>
       <c r="N6">
-        <v>4.814429333333334</v>
+        <v>4.689608333333334</v>
       </c>
       <c r="O6">
-        <v>0.9147415733333335</v>
+        <v>0.8910255833333335</v>
       </c>
       <c r="P6">
-        <v>3.89968776</v>
+        <v>3.79858275</v>
       </c>
       <c r="Q6">
-        <v>5.739687760000001</v>
+        <v>5.63858275</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07768240065958089</v>
+        <v>0.07795632187698326</v>
       </c>
       <c r="T6">
-        <v>0.5839373647168578</v>
+        <v>0.5889543280107402</v>
       </c>
       <c r="U6">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V6">
         <v>0.19</v>
       </c>
       <c r="W6">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>12.22495787713179</v>
+        <v>9.469201017352177</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07622525578313409</v>
+        <v>0.07614200693307054</v>
       </c>
       <c r="C7">
-        <v>203.6207172794878</v>
+        <v>202.1170977390672</v>
       </c>
       <c r="D7">
-        <v>206.4307172794878</v>
+        <v>206.9970977390672</v>
       </c>
       <c r="E7">
-        <v>-58.45</v>
+        <v>-56.38</v>
       </c>
       <c r="F7">
-        <v>10.35</v>
+        <v>12.42</v>
       </c>
       <c r="G7">
         <v>7.54</v>
@@ -1849,28 +1849,28 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M7">
-        <v>0.553725</v>
+        <v>0.6644700000000001</v>
       </c>
       <c r="N7">
-        <v>4.689608333333334</v>
+        <v>4.578863333333334</v>
       </c>
       <c r="O7">
-        <v>0.8910255833333335</v>
+        <v>0.8699840333333335</v>
       </c>
       <c r="P7">
-        <v>3.79858275</v>
+        <v>3.708879300000001</v>
       </c>
       <c r="Q7">
-        <v>5.63858275</v>
+        <v>5.548879300000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07795632187698326</v>
+        <v>0.07823607120539419</v>
       </c>
       <c r="T7">
-        <v>0.5889543280107402</v>
+        <v>0.5940780352044926</v>
       </c>
       <c r="U7">
         <v>0.0535</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>9.469201017352177</v>
+        <v>7.89100084779348</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07614200693307054</v>
+        <v>0.07610411808300699</v>
       </c>
       <c r="C8">
-        <v>202.1170977390672</v>
+        <v>200.3059035547765</v>
       </c>
       <c r="D8">
-        <v>206.9970977390672</v>
+        <v>207.2559035547765</v>
       </c>
       <c r="E8">
-        <v>-56.38</v>
+        <v>-54.31</v>
       </c>
       <c r="F8">
-        <v>12.42</v>
+        <v>14.49</v>
       </c>
       <c r="G8">
         <v>7.54</v>
@@ -1931,45 +1931,45 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M8">
-        <v>0.66447</v>
+        <v>0.7868069999999999</v>
       </c>
       <c r="N8">
-        <v>4.578863333333334</v>
+        <v>4.456526333333334</v>
       </c>
       <c r="O8">
-        <v>0.8699840333333335</v>
+        <v>0.8467400033333335</v>
       </c>
       <c r="P8">
-        <v>3.708879300000001</v>
+        <v>3.609786330000001</v>
       </c>
       <c r="Q8">
-        <v>5.548879300000001</v>
+        <v>5.44978633</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07823607120539419</v>
+        <v>0.0785218366483946</v>
       </c>
       <c r="T8">
-        <v>0.5940780352044926</v>
+        <v>0.5993119296497236</v>
       </c>
       <c r="U8">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V8">
         <v>0.19</v>
       </c>
       <c r="W8">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>7.891000847793481</v>
+        <v>6.664065435784551</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07610411808300697</v>
+        <v>0.07609214923294344</v>
       </c>
       <c r="C9">
-        <v>200.3059035547766</v>
+        <v>198.3177932488803</v>
       </c>
       <c r="D9">
-        <v>207.2559035547766</v>
+        <v>207.3377932488803</v>
       </c>
       <c r="E9">
-        <v>-54.31</v>
+        <v>-52.23999999999999</v>
       </c>
       <c r="F9">
-        <v>14.49</v>
+        <v>16.56</v>
       </c>
       <c r="G9">
         <v>7.54</v>
@@ -2013,45 +2013,45 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M9">
-        <v>0.7868070000000001</v>
+        <v>0.9157679999999999</v>
       </c>
       <c r="N9">
-        <v>4.456526333333334</v>
+        <v>4.327565333333334</v>
       </c>
       <c r="O9">
-        <v>0.8467400033333334</v>
+        <v>0.8222374133333334</v>
       </c>
       <c r="P9">
-        <v>3.60978633</v>
+        <v>3.505327920000001</v>
       </c>
       <c r="Q9">
-        <v>5.44978633</v>
+        <v>5.345327920000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0785218366483946</v>
+        <v>0.07881381438363416</v>
       </c>
       <c r="T9">
-        <v>0.5993119296497236</v>
+        <v>0.6046596044089813</v>
       </c>
       <c r="U9">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V9">
         <v>0.19</v>
       </c>
       <c r="W9">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y9">
-        <v>6.664065435784548</v>
+        <v>5.72561318296046</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07609214923294344</v>
+        <v>0.07602348038287987</v>
       </c>
       <c r="C10">
-        <v>198.3177932488803</v>
+        <v>196.7188722793808</v>
       </c>
       <c r="D10">
-        <v>207.3377932488803</v>
+        <v>207.8088722793808</v>
       </c>
       <c r="E10">
-        <v>-52.23999999999999</v>
+        <v>-50.17</v>
       </c>
       <c r="F10">
-        <v>16.56</v>
+        <v>18.63</v>
       </c>
       <c r="G10">
         <v>7.54</v>
@@ -2095,28 +2095,28 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M10">
-        <v>0.9157679999999999</v>
+        <v>1.030239</v>
       </c>
       <c r="N10">
-        <v>4.327565333333334</v>
+        <v>4.213094333333334</v>
       </c>
       <c r="O10">
-        <v>0.8222374133333334</v>
+        <v>0.8004879233333335</v>
       </c>
       <c r="P10">
-        <v>3.505327920000001</v>
+        <v>3.41260641</v>
       </c>
       <c r="Q10">
-        <v>5.345327920000001</v>
+        <v>5.25260641</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07881381438363416</v>
+        <v>0.07911220921195589</v>
       </c>
       <c r="T10">
-        <v>0.6046596044089813</v>
+        <v>0.610124810481629</v>
       </c>
       <c r="U10">
         <v>0.0553</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>5.72561318296046</v>
+        <v>5.089433940409298</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07602348038287987</v>
+        <v>0.07595481153281632</v>
       </c>
       <c r="C11">
-        <v>196.7188722793808</v>
+        <v>195.1220968020047</v>
       </c>
       <c r="D11">
-        <v>207.8088722793808</v>
+        <v>208.2820968020047</v>
       </c>
       <c r="E11">
-        <v>-50.17</v>
+        <v>-48.09999999999999</v>
       </c>
       <c r="F11">
-        <v>18.63</v>
+        <v>20.7</v>
       </c>
       <c r="G11">
         <v>7.54</v>
@@ -2177,28 +2177,28 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M11">
-        <v>1.030239</v>
+        <v>1.14471</v>
       </c>
       <c r="N11">
-        <v>4.213094333333334</v>
+        <v>4.098623333333334</v>
       </c>
       <c r="O11">
-        <v>0.8004879233333335</v>
+        <v>0.7787384333333335</v>
       </c>
       <c r="P11">
-        <v>3.41260641</v>
+        <v>3.319884900000001</v>
       </c>
       <c r="Q11">
-        <v>5.25260641</v>
+        <v>5.159884900000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07911220921195589</v>
+        <v>0.07941723503646256</v>
       </c>
       <c r="T11">
-        <v>0.610124810481629</v>
+        <v>0.6157114655781137</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>5.089433940409298</v>
+        <v>4.580490546368368</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07595481153281632</v>
+        <v>0.07642074268275274</v>
       </c>
       <c r="C12">
-        <v>195.1220968020046</v>
+        <v>189.88283608617</v>
       </c>
       <c r="D12">
-        <v>208.2820968020047</v>
+        <v>205.1128360861701</v>
       </c>
       <c r="E12">
-        <v>-48.09999999999999</v>
+        <v>-46.03</v>
       </c>
       <c r="F12">
-        <v>20.7</v>
+        <v>22.77</v>
       </c>
       <c r="G12">
         <v>7.54</v>
@@ -2259,45 +2259,45 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M12">
-        <v>1.14471</v>
+        <v>1.395801</v>
       </c>
       <c r="N12">
-        <v>4.098623333333334</v>
+        <v>3.847532333333334</v>
       </c>
       <c r="O12">
-        <v>0.7787384333333335</v>
+        <v>0.7310311433333335</v>
       </c>
       <c r="P12">
-        <v>3.319884900000001</v>
+        <v>3.116501190000001</v>
       </c>
       <c r="Q12">
-        <v>5.159884900000001</v>
+        <v>4.956501190000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07941723503646256</v>
+        <v>0.07972911537387949</v>
       </c>
       <c r="T12">
-        <v>0.6157114655781137</v>
+        <v>0.6214236634857552</v>
       </c>
       <c r="U12">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V12">
         <v>0.19</v>
       </c>
       <c r="W12">
-        <v>0.04479300000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.580490546368367</v>
+        <v>3.756504926800693</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07642074268275274</v>
+        <v>0.07667283383268919</v>
       </c>
       <c r="C13">
-        <v>189.88283608617</v>
+        <v>186.1379936989792</v>
       </c>
       <c r="D13">
-        <v>205.1128360861701</v>
+        <v>203.4379936989792</v>
       </c>
       <c r="E13">
-        <v>-46.03</v>
+        <v>-43.95999999999999</v>
       </c>
       <c r="F13">
-        <v>22.77</v>
+        <v>24.84</v>
       </c>
       <c r="G13">
         <v>7.54</v>
@@ -2341,45 +2341,45 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M13">
-        <v>1.395801</v>
+        <v>1.592244</v>
       </c>
       <c r="N13">
-        <v>3.847532333333334</v>
+        <v>3.651089333333334</v>
       </c>
       <c r="O13">
-        <v>0.7310311433333335</v>
+        <v>0.6937069733333335</v>
       </c>
       <c r="P13">
-        <v>3.116501190000001</v>
+        <v>2.95738236</v>
       </c>
       <c r="Q13">
-        <v>4.956501190000001</v>
+        <v>4.79738236</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07972911537387949</v>
+        <v>0.08004808390078316</v>
       </c>
       <c r="T13">
-        <v>0.6214236634857552</v>
+        <v>0.6272656840731158</v>
       </c>
       <c r="U13">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V13">
         <v>0.19</v>
       </c>
       <c r="W13">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y13">
-        <v>3.756504926800693</v>
+        <v>3.293046375639245</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07667283383268919</v>
+        <v>0.07667544498262562</v>
       </c>
       <c r="C14">
-        <v>186.1379936989792</v>
+        <v>184.0507888585433</v>
       </c>
       <c r="D14">
-        <v>203.4379936989792</v>
+        <v>203.4207888585433</v>
       </c>
       <c r="E14">
-        <v>-43.95999999999999</v>
+        <v>-41.89</v>
       </c>
       <c r="F14">
-        <v>24.84</v>
+        <v>26.91</v>
       </c>
       <c r="G14">
         <v>7.54</v>
@@ -2423,28 +2423,28 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M14">
-        <v>1.592244</v>
+        <v>1.724931</v>
       </c>
       <c r="N14">
-        <v>3.651089333333334</v>
+        <v>3.518402333333334</v>
       </c>
       <c r="O14">
-        <v>0.6937069733333335</v>
+        <v>0.6684964433333335</v>
       </c>
       <c r="P14">
-        <v>2.95738236</v>
+        <v>2.84990589</v>
       </c>
       <c r="Q14">
-        <v>4.79738236</v>
+        <v>4.68990589</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08004808390078316</v>
+        <v>0.08037438503750072</v>
       </c>
       <c r="T14">
-        <v>0.6272656840731158</v>
+        <v>0.6332420039843238</v>
       </c>
       <c r="U14">
         <v>0.0641</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>3.293046375639245</v>
+        <v>3.039735115974687</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07667544498262562</v>
+        <v>0.07756257613256207</v>
       </c>
       <c r="C15">
-        <v>184.0507888585433</v>
+        <v>176.2992308643837</v>
       </c>
       <c r="D15">
-        <v>203.4207888585433</v>
+        <v>197.7392308643837</v>
       </c>
       <c r="E15">
-        <v>-41.89</v>
+        <v>-39.81999999999999</v>
       </c>
       <c r="F15">
-        <v>26.91</v>
+        <v>28.98</v>
       </c>
       <c r="G15">
         <v>7.54</v>
@@ -2505,45 +2505,45 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M15">
-        <v>1.724931</v>
+        <v>2.083662</v>
       </c>
       <c r="N15">
-        <v>3.518402333333334</v>
+        <v>3.159671333333334</v>
       </c>
       <c r="O15">
-        <v>0.6684964433333335</v>
+        <v>0.6003375533333334</v>
       </c>
       <c r="P15">
-        <v>2.84990589</v>
+        <v>2.55933378</v>
       </c>
       <c r="Q15">
-        <v>4.68990589</v>
+        <v>4.39933378</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08037438503750072</v>
+        <v>0.0807082745727466</v>
       </c>
       <c r="T15">
-        <v>0.6332420039843238</v>
+        <v>0.6393573080795134</v>
       </c>
       <c r="U15">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V15">
         <v>0.19</v>
       </c>
       <c r="W15">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>3.039735115974687</v>
+        <v>2.516403012260786</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07756257613256207</v>
+        <v>0.07810221728249853</v>
       </c>
       <c r="C16">
-        <v>176.2992308643837</v>
+        <v>170.9257973880377</v>
       </c>
       <c r="D16">
-        <v>197.7392308643837</v>
+        <v>194.4357973880377</v>
       </c>
       <c r="E16">
-        <v>-39.81999999999999</v>
+        <v>-37.74999999999999</v>
       </c>
       <c r="F16">
-        <v>28.98</v>
+        <v>31.05</v>
       </c>
       <c r="G16">
         <v>7.54</v>
@@ -2587,45 +2587,45 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M16">
-        <v>2.083662</v>
+        <v>2.353590000000001</v>
       </c>
       <c r="N16">
-        <v>3.159671333333334</v>
+        <v>2.889743333333334</v>
       </c>
       <c r="O16">
-        <v>0.6003375533333334</v>
+        <v>0.5490512333333334</v>
       </c>
       <c r="P16">
-        <v>2.55933378</v>
+        <v>2.3406921</v>
       </c>
       <c r="Q16">
-        <v>4.39933378</v>
+        <v>4.1806921</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0807082745727466</v>
+        <v>0.0810500203323512</v>
       </c>
       <c r="T16">
-        <v>0.6393573080795134</v>
+        <v>0.6456165016828251</v>
       </c>
       <c r="U16">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V16">
         <v>0.19</v>
       </c>
       <c r="W16">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y16">
-        <v>2.516403012260786</v>
+        <v>2.227802350168608</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07810221728249853</v>
+        <v>0.07819959843243496</v>
       </c>
       <c r="C17">
-        <v>170.9257973880377</v>
+        <v>168.2713956529996</v>
       </c>
       <c r="D17">
-        <v>194.4357973880377</v>
+        <v>193.8513956529996</v>
       </c>
       <c r="E17">
-        <v>-37.75</v>
+        <v>-35.68</v>
       </c>
       <c r="F17">
-        <v>31.05</v>
+        <v>33.12</v>
       </c>
       <c r="G17">
         <v>7.54</v>
@@ -2669,28 +2669,28 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M17">
-        <v>2.35359</v>
+        <v>2.510496</v>
       </c>
       <c r="N17">
-        <v>2.889743333333334</v>
+        <v>2.732837333333334</v>
       </c>
       <c r="O17">
-        <v>0.5490512333333335</v>
+        <v>0.5192390933333335</v>
       </c>
       <c r="P17">
-        <v>2.3406921</v>
+        <v>2.21359824</v>
       </c>
       <c r="Q17">
-        <v>4.1806921</v>
+        <v>4.05359824</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0810500203323512</v>
+        <v>0.0813999028957559</v>
       </c>
       <c r="T17">
-        <v>0.6456165016828251</v>
+        <v>0.6520247237052632</v>
       </c>
       <c r="U17">
         <v>0.07580000000000001</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>2.227802350168608</v>
+        <v>2.08856470328307</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07819959843243496</v>
+        <v>0.08025231958237139</v>
       </c>
       <c r="C18">
-        <v>168.2713956529996</v>
+        <v>154.6514371995428</v>
       </c>
       <c r="D18">
-        <v>193.8513956529996</v>
+        <v>182.3014371995428</v>
       </c>
       <c r="E18">
-        <v>-35.68</v>
+        <v>-33.60999999999999</v>
       </c>
       <c r="F18">
-        <v>33.12</v>
+        <v>35.19</v>
       </c>
       <c r="G18">
         <v>7.54</v>
@@ -2751,45 +2751,45 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M18">
-        <v>2.510496</v>
+        <v>3.1671</v>
       </c>
       <c r="N18">
-        <v>2.732837333333334</v>
+        <v>2.076233333333334</v>
       </c>
       <c r="O18">
-        <v>0.5192390933333335</v>
+        <v>0.3944843333333334</v>
       </c>
       <c r="P18">
-        <v>2.21359824</v>
+        <v>1.681749</v>
       </c>
       <c r="Q18">
-        <v>4.05359824</v>
+        <v>3.521749</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0813999028957559</v>
+        <v>0.08175821636430289</v>
       </c>
       <c r="T18">
-        <v>0.6520247237052632</v>
+        <v>0.6585873607161939</v>
       </c>
       <c r="U18">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V18">
         <v>0.19</v>
       </c>
       <c r="W18">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>2.08856470328307</v>
+        <v>1.655562922968436</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08025231958237139</v>
+        <v>0.08046472073230783</v>
       </c>
       <c r="C19">
-        <v>154.6514371995428</v>
+        <v>151.4644215687155</v>
       </c>
       <c r="D19">
-        <v>182.3014371995428</v>
+        <v>181.1844215687155</v>
       </c>
       <c r="E19">
-        <v>-33.60999999999999</v>
+        <v>-31.53999999999999</v>
       </c>
       <c r="F19">
-        <v>35.19</v>
+        <v>37.26000000000001</v>
       </c>
       <c r="G19">
         <v>7.54</v>
@@ -2833,28 +2833,28 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M19">
-        <v>3.1671</v>
+        <v>3.3534</v>
       </c>
       <c r="N19">
-        <v>2.076233333333334</v>
+        <v>1.889933333333334</v>
       </c>
       <c r="O19">
-        <v>0.3944843333333334</v>
+        <v>0.3590873333333334</v>
       </c>
       <c r="P19">
-        <v>1.681749</v>
+        <v>1.530846</v>
       </c>
       <c r="Q19">
-        <v>3.521749</v>
+        <v>3.370846</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08175821636430289</v>
+        <v>0.08212526918574126</v>
       </c>
       <c r="T19">
-        <v>0.6585873607161939</v>
+        <v>0.6653100620444642</v>
       </c>
       <c r="U19">
         <v>0.09</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>1.655562922968436</v>
+        <v>1.563587205025745</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08046472073230783</v>
+        <v>0.09000766453092258</v>
       </c>
       <c r="C20">
-        <v>151.4644215687156</v>
+        <v>110.282815684054</v>
       </c>
       <c r="D20">
-        <v>181.1844215687155</v>
+        <v>142.072815684054</v>
       </c>
       <c r="E20">
-        <v>-31.54</v>
+        <v>-29.47</v>
       </c>
       <c r="F20">
-        <v>37.26</v>
+        <v>39.33</v>
       </c>
       <c r="G20">
         <v>7.54</v>
@@ -2915,45 +2915,45 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M20">
-        <v>3.3534</v>
+        <v>5.773644</v>
       </c>
       <c r="N20">
-        <v>1.889933333333334</v>
+        <v>-0.5303106666666659</v>
       </c>
       <c r="O20">
-        <v>0.3590873333333335</v>
+        <v>-0.1007590266666665</v>
       </c>
       <c r="P20">
-        <v>1.530846000000001</v>
+        <v>-0.4295516399999994</v>
       </c>
       <c r="Q20">
-        <v>3.370846000000001</v>
+        <v>1.41044836</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08212526918574126</v>
+        <v>0.08262763697282942</v>
       </c>
       <c r="T20">
-        <v>0.6653100620444642</v>
+        <v>0.6745111044892635</v>
       </c>
       <c r="U20">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V20">
-        <v>0.19</v>
+        <v>0.1725484517807702</v>
       </c>
       <c r="W20">
-        <v>0.07290000000000001</v>
+        <v>0.1214698872785829</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y20">
-        <v>1.563587205025745</v>
+        <v>0.9081497462145802</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09000766453092258</v>
+        <v>0.09101766453092261</v>
       </c>
       <c r="C21">
-        <v>110.282815684054</v>
+        <v>105.0394199474659</v>
       </c>
       <c r="D21">
-        <v>142.072815684054</v>
+        <v>138.899419947466</v>
       </c>
       <c r="E21">
-        <v>-29.47</v>
+        <v>-27.39999999999999</v>
       </c>
       <c r="F21">
-        <v>39.33</v>
+        <v>41.40000000000001</v>
       </c>
       <c r="G21">
         <v>7.54</v>
@@ -2997,37 +2997,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M21">
-        <v>5.773644</v>
+        <v>6.077520000000002</v>
       </c>
       <c r="N21">
-        <v>-0.5303106666666659</v>
+        <v>-0.8341866666666675</v>
       </c>
       <c r="O21">
-        <v>-0.1007590266666665</v>
+        <v>-0.1584954666666668</v>
       </c>
       <c r="P21">
-        <v>-0.4295516399999994</v>
+        <v>-0.6756912000000007</v>
       </c>
       <c r="Q21">
-        <v>1.41044836</v>
+        <v>1.164308799999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08262763697282942</v>
+        <v>0.0830879824349898</v>
       </c>
       <c r="T21">
-        <v>0.6745111044892635</v>
+        <v>0.6829424932953794</v>
       </c>
       <c r="U21">
         <v>0.1468</v>
       </c>
       <c r="V21">
-        <v>0.1725484517807702</v>
+        <v>0.1639210291917317</v>
       </c>
       <c r="W21">
-        <v>0.1214698872785829</v>
+        <v>0.1227363929146538</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.9081497462145802</v>
+        <v>0.862742258903851</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09101766453092261</v>
+        <v>0.09202766453092261</v>
       </c>
       <c r="C22">
-        <v>105.0394199474659</v>
+        <v>99.93469138026569</v>
       </c>
       <c r="D22">
-        <v>138.899419947466</v>
+        <v>135.8646913802657</v>
       </c>
       <c r="E22">
-        <v>-27.39999999999999</v>
+        <v>-25.32999999999999</v>
       </c>
       <c r="F22">
-        <v>41.40000000000001</v>
+        <v>43.47000000000001</v>
       </c>
       <c r="G22">
         <v>7.54</v>
@@ -3079,37 +3079,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M22">
-        <v>6.077520000000002</v>
+        <v>6.381396000000001</v>
       </c>
       <c r="N22">
-        <v>-0.8341866666666675</v>
+        <v>-1.138062666666667</v>
       </c>
       <c r="O22">
-        <v>-0.1584954666666668</v>
+        <v>-0.2162319066666668</v>
       </c>
       <c r="P22">
-        <v>-0.6756912000000007</v>
+        <v>-0.9218307600000005</v>
       </c>
       <c r="Q22">
-        <v>1.164308799999999</v>
+        <v>0.9181692399999993</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0830879824349898</v>
+        <v>0.0835599822126479</v>
       </c>
       <c r="T22">
-        <v>0.6829424932953794</v>
+        <v>0.6915873349826628</v>
       </c>
       <c r="U22">
         <v>0.1468</v>
       </c>
       <c r="V22">
-        <v>0.1639210291917317</v>
+        <v>0.1561152658968873</v>
       </c>
       <c r="W22">
-        <v>0.1227363929146538</v>
+        <v>0.1238822789663369</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.862742258903851</v>
+        <v>0.8216592941941439</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09202766453092259</v>
+        <v>0.1051895776813949</v>
       </c>
       <c r="C23">
-        <v>99.93469138026575</v>
+        <v>67.75437004145971</v>
       </c>
       <c r="D23">
-        <v>135.8646913802658</v>
+        <v>105.7543700414597</v>
       </c>
       <c r="E23">
-        <v>-25.33</v>
+        <v>-23.26</v>
       </c>
       <c r="F23">
-        <v>43.47</v>
+        <v>45.54</v>
       </c>
       <c r="G23">
         <v>7.54</v>
@@ -3161,45 +3161,45 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M23">
-        <v>6.381396000000001</v>
+        <v>9.144432</v>
       </c>
       <c r="N23">
-        <v>-1.138062666666666</v>
+        <v>-3.901098666666666</v>
       </c>
       <c r="O23">
-        <v>-0.2162319066666666</v>
+        <v>-0.7412087466666666</v>
       </c>
       <c r="P23">
-        <v>-0.9218307599999997</v>
+        <v>-3.159889919999999</v>
       </c>
       <c r="Q23">
-        <v>0.9181692400000001</v>
+        <v>-1.31988992</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0835599822126479</v>
+        <v>0.08439269115187713</v>
       </c>
       <c r="T23">
-        <v>0.6915873349826628</v>
+        <v>0.7068386916399465</v>
       </c>
       <c r="U23">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V23">
-        <v>0.1561152658968873</v>
+        <v>0.1089442551853777</v>
       </c>
       <c r="W23">
-        <v>0.1238822789663369</v>
+        <v>0.1789239935587762</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y23">
-        <v>0.821659294194144</v>
+        <v>0.5733908167651456</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1051895776813949</v>
+        <v>0.1067395776813949</v>
       </c>
       <c r="C24">
-        <v>67.75437004145971</v>
+        <v>62.99450444341984</v>
       </c>
       <c r="D24">
-        <v>105.7543700414597</v>
+        <v>103.0645044434198</v>
       </c>
       <c r="E24">
-        <v>-23.26</v>
+        <v>-21.19</v>
       </c>
       <c r="F24">
-        <v>45.54</v>
+        <v>47.61</v>
       </c>
       <c r="G24">
         <v>7.54</v>
@@ -3243,37 +3243,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M24">
-        <v>9.144432</v>
+        <v>9.560088</v>
       </c>
       <c r="N24">
-        <v>-3.901098666666666</v>
+        <v>-4.316754666666666</v>
       </c>
       <c r="O24">
-        <v>-0.7412087466666666</v>
+        <v>-0.8201833866666666</v>
       </c>
       <c r="P24">
-        <v>-3.159889919999999</v>
+        <v>-3.49657128</v>
       </c>
       <c r="Q24">
-        <v>-1.31988992</v>
+        <v>-1.65657128</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08439269115187713</v>
+        <v>0.08489389493307034</v>
       </c>
       <c r="T24">
-        <v>0.7068386916399465</v>
+        <v>0.7160184149079978</v>
       </c>
       <c r="U24">
         <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.1089442551853777</v>
+        <v>0.1042075484381873</v>
       </c>
       <c r="W24">
-        <v>0.1789239935587762</v>
+        <v>0.179875124273612</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.5733908167651456</v>
+        <v>0.5484607812536175</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1067395776813949</v>
+        <v>0.1082895776813949</v>
       </c>
       <c r="C25">
-        <v>62.99450444341984</v>
+        <v>58.36807843104076</v>
       </c>
       <c r="D25">
-        <v>103.0645044434198</v>
+        <v>100.5080784310408</v>
       </c>
       <c r="E25">
-        <v>-21.19</v>
+        <v>-19.11999999999999</v>
       </c>
       <c r="F25">
-        <v>47.61</v>
+        <v>49.68000000000001</v>
       </c>
       <c r="G25">
         <v>7.54</v>
@@ -3325,37 +3325,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M25">
-        <v>9.560088</v>
+        <v>9.975744000000002</v>
       </c>
       <c r="N25">
-        <v>-4.316754666666666</v>
+        <v>-4.732410666666668</v>
       </c>
       <c r="O25">
-        <v>-0.8201833866666666</v>
+        <v>-0.899158026666667</v>
       </c>
       <c r="P25">
-        <v>-3.49657128</v>
+        <v>-3.833252640000001</v>
       </c>
       <c r="Q25">
-        <v>-1.65657128</v>
+        <v>-1.993252640000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08489389493307034</v>
+        <v>0.08540828828745284</v>
       </c>
       <c r="T25">
-        <v>0.7160184149079978</v>
+        <v>0.7254397098409978</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.1042075484381873</v>
+        <v>0.09986556725326283</v>
       </c>
       <c r="W25">
-        <v>0.179875124273612</v>
+        <v>0.1807469940955448</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.5484607812536175</v>
+        <v>0.5256082487013833</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1082895776813949</v>
+        <v>0.1098395776813949</v>
       </c>
       <c r="C26">
-        <v>58.36807843104078</v>
+        <v>53.86540277625778</v>
       </c>
       <c r="D26">
-        <v>100.5080784310408</v>
+        <v>98.07540277625777</v>
       </c>
       <c r="E26">
-        <v>-19.12</v>
+        <v>-17.05</v>
       </c>
       <c r="F26">
-        <v>49.68</v>
+        <v>51.75</v>
       </c>
       <c r="G26">
         <v>7.54</v>
@@ -3407,37 +3407,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M26">
-        <v>9.975744000000001</v>
+        <v>10.3914</v>
       </c>
       <c r="N26">
-        <v>-4.732410666666667</v>
+        <v>-5.148066666666667</v>
       </c>
       <c r="O26">
-        <v>-0.8991580266666667</v>
+        <v>-0.9781326666666667</v>
       </c>
       <c r="P26">
-        <v>-3.83325264</v>
+        <v>-4.169934</v>
       </c>
       <c r="Q26">
-        <v>-1.99325264</v>
+        <v>-2.329934000000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08540828828745284</v>
+        <v>0.0859363987979522</v>
       </c>
       <c r="T26">
-        <v>0.7254397098409978</v>
+        <v>0.7351122393055444</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.09986556725326286</v>
+        <v>0.09587094456313233</v>
       </c>
       <c r="W26">
-        <v>0.1807469940955448</v>
+        <v>0.181549114331723</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.5256082487013835</v>
+        <v>0.5045839187533281</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1098395776813949</v>
+        <v>0.1205992979219571</v>
       </c>
       <c r="C27">
-        <v>53.86540277625778</v>
+        <v>37.68746425718218</v>
       </c>
       <c r="D27">
-        <v>98.07540277625777</v>
+        <v>83.96746425718217</v>
       </c>
       <c r="E27">
-        <v>-17.05</v>
+        <v>-14.98</v>
       </c>
       <c r="F27">
-        <v>51.75</v>
+        <v>53.82</v>
       </c>
       <c r="G27">
         <v>7.54</v>
@@ -3489,45 +3489,45 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M27">
-        <v>10.3914</v>
+        <v>12.690756</v>
       </c>
       <c r="N27">
-        <v>-5.148066666666667</v>
+        <v>-7.447422666666666</v>
       </c>
       <c r="O27">
-        <v>-0.9781326666666667</v>
+        <v>-1.415010306666667</v>
       </c>
       <c r="P27">
-        <v>-4.169934</v>
+        <v>-6.032412359999999</v>
       </c>
       <c r="Q27">
-        <v>-2.329934000000001</v>
+        <v>-4.19241236</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0859363987979522</v>
+        <v>0.08662705316084646</v>
       </c>
       <c r="T27">
-        <v>0.7351122393055444</v>
+        <v>0.7477618165097463</v>
       </c>
       <c r="U27">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.09587094456313233</v>
+        <v>0.07850070817950747</v>
       </c>
       <c r="W27">
-        <v>0.181549114331723</v>
+        <v>0.2172895330112721</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y27">
-        <v>0.5045839187533281</v>
+        <v>0.4131616219974077</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1205992979219571</v>
+        <v>0.1224992979219571</v>
       </c>
       <c r="C28">
-        <v>37.68746425718218</v>
+        <v>33.53741676768651</v>
       </c>
       <c r="D28">
-        <v>83.96746425718217</v>
+        <v>81.8874167676865</v>
       </c>
       <c r="E28">
-        <v>-14.98</v>
+        <v>-12.91</v>
       </c>
       <c r="F28">
-        <v>53.82</v>
+        <v>55.89</v>
       </c>
       <c r="G28">
         <v>7.54</v>
@@ -3571,37 +3571,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M28">
-        <v>12.690756</v>
+        <v>13.178862</v>
       </c>
       <c r="N28">
-        <v>-7.447422666666666</v>
+        <v>-7.935528666666666</v>
       </c>
       <c r="O28">
-        <v>-1.415010306666667</v>
+        <v>-1.507750446666667</v>
       </c>
       <c r="P28">
-        <v>-6.032412359999999</v>
+        <v>-6.42777822</v>
       </c>
       <c r="Q28">
-        <v>-4.19241236</v>
+        <v>-4.58777822</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08662705316084646</v>
+        <v>0.08718632786167997</v>
       </c>
       <c r="T28">
-        <v>0.7477618165097463</v>
+        <v>0.7580051290646743</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.07850070817950747</v>
+        <v>0.07559327454322941</v>
       </c>
       <c r="W28">
-        <v>0.2172895330112721</v>
+        <v>0.2179751058627065</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.4131616219974077</v>
+        <v>0.3978593397012075</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1224992979219571</v>
+        <v>0.1243992979219571</v>
       </c>
       <c r="C29">
-        <v>33.53741676768651</v>
+        <v>29.48793226881615</v>
       </c>
       <c r="D29">
-        <v>81.8874167676865</v>
+        <v>79.90793226881615</v>
       </c>
       <c r="E29">
-        <v>-12.91</v>
+        <v>-10.83999999999999</v>
       </c>
       <c r="F29">
-        <v>55.89</v>
+        <v>57.96000000000001</v>
       </c>
       <c r="G29">
         <v>7.54</v>
@@ -3653,37 +3653,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M29">
-        <v>13.178862</v>
+        <v>13.666968</v>
       </c>
       <c r="N29">
-        <v>-7.935528666666666</v>
+        <v>-8.423634666666668</v>
       </c>
       <c r="O29">
-        <v>-1.507750446666667</v>
+        <v>-1.600490586666667</v>
       </c>
       <c r="P29">
-        <v>-6.42777822</v>
+        <v>-6.823144080000001</v>
       </c>
       <c r="Q29">
-        <v>-4.58777822</v>
+        <v>-4.983144080000002</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08718632786167997</v>
+        <v>0.08776113797086997</v>
       </c>
       <c r="T29">
-        <v>0.7580051290646743</v>
+        <v>0.7685329780794614</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.07559327454322941</v>
+        <v>0.07289351473811406</v>
       </c>
       <c r="W29">
-        <v>0.2179751058627065</v>
+        <v>0.2186117092247527</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3978593397012075</v>
+        <v>0.3836500775690214</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1243992979219571</v>
+        <v>0.1262992979219572</v>
       </c>
       <c r="C30">
-        <v>29.48793226881615</v>
+        <v>25.53189008919437</v>
       </c>
       <c r="D30">
-        <v>79.90793226881615</v>
+        <v>78.02189008919437</v>
       </c>
       <c r="E30">
-        <v>-10.83999999999999</v>
+        <v>-8.769999999999989</v>
       </c>
       <c r="F30">
-        <v>57.96000000000001</v>
+        <v>60.03000000000001</v>
       </c>
       <c r="G30">
         <v>7.54</v>
@@ -3735,37 +3735,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M30">
-        <v>13.666968</v>
+        <v>14.155074</v>
       </c>
       <c r="N30">
-        <v>-8.423634666666668</v>
+        <v>-8.911740666666669</v>
       </c>
       <c r="O30">
-        <v>-1.600490586666667</v>
+        <v>-1.693230726666667</v>
       </c>
       <c r="P30">
-        <v>-6.823144080000001</v>
+        <v>-7.218509940000001</v>
       </c>
       <c r="Q30">
-        <v>-4.983144080000002</v>
+        <v>-5.378509940000002</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08776113797086997</v>
+        <v>0.08835213991412166</v>
       </c>
       <c r="T30">
-        <v>0.7685329780794614</v>
+        <v>0.7793573862214257</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.07289351473811406</v>
+        <v>0.070379945264386</v>
       </c>
       <c r="W30">
-        <v>0.2186117092247527</v>
+        <v>0.2192044089066578</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3836500775690214</v>
+        <v>0.3704207645494</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1262992979219571</v>
+        <v>0.1281992979219571</v>
       </c>
       <c r="C31">
-        <v>25.53189008919441</v>
+        <v>21.66282632399249</v>
       </c>
       <c r="D31">
-        <v>78.0218900891944</v>
+        <v>76.22282632399248</v>
       </c>
       <c r="E31">
-        <v>-8.770000000000003</v>
+        <v>-6.700000000000003</v>
       </c>
       <c r="F31">
-        <v>60.02999999999999</v>
+        <v>62.09999999999999</v>
       </c>
       <c r="G31">
         <v>7.54</v>
@@ -3817,37 +3817,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M31">
-        <v>14.155074</v>
+        <v>14.64318</v>
       </c>
       <c r="N31">
-        <v>-8.911740666666665</v>
+        <v>-9.399846666666665</v>
       </c>
       <c r="O31">
-        <v>-1.693230726666666</v>
+        <v>-1.785970866666666</v>
       </c>
       <c r="P31">
-        <v>-7.218509939999999</v>
+        <v>-7.613875799999999</v>
       </c>
       <c r="Q31">
-        <v>-5.378509939999999</v>
+        <v>-5.773875799999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08835213991412166</v>
+        <v>0.08896002762718053</v>
       </c>
       <c r="T31">
-        <v>0.7793573862214256</v>
+        <v>0.790491063167446</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.07037994526438601</v>
+        <v>0.06803394708890648</v>
       </c>
       <c r="W31">
-        <v>0.2192044089066578</v>
+        <v>0.2197575952764359</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3704207645494001</v>
+        <v>0.3580734057310867</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1281992979219571</v>
+        <v>0.1300992979219571</v>
       </c>
       <c r="C32">
-        <v>21.66282632399249</v>
+        <v>17.87485982147595</v>
       </c>
       <c r="D32">
-        <v>76.22282632399248</v>
+        <v>74.50485982147595</v>
       </c>
       <c r="E32">
-        <v>-6.700000000000003</v>
+        <v>-4.629999999999995</v>
       </c>
       <c r="F32">
-        <v>62.09999999999999</v>
+        <v>64.17</v>
       </c>
       <c r="G32">
         <v>7.54</v>
@@ -3899,37 +3899,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M32">
-        <v>14.64318</v>
+        <v>15.131286</v>
       </c>
       <c r="N32">
-        <v>-9.399846666666665</v>
+        <v>-9.887952666666667</v>
       </c>
       <c r="O32">
-        <v>-1.785970866666666</v>
+        <v>-1.878711006666667</v>
       </c>
       <c r="P32">
-        <v>-7.613875799999999</v>
+        <v>-8.009241660000001</v>
       </c>
       <c r="Q32">
-        <v>-5.773875799999999</v>
+        <v>-6.169241660000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08896002762718053</v>
+        <v>0.08958553527395127</v>
       </c>
       <c r="T32">
-        <v>0.790491063167446</v>
+        <v>0.8019474553872642</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.06803394708890648</v>
+        <v>0.06583930363442561</v>
       </c>
       <c r="W32">
-        <v>0.2197575952764359</v>
+        <v>0.2202750922030025</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3580734057310867</v>
+        <v>0.3465226507075032</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1300992979219571</v>
+        <v>0.1319992979219571</v>
       </c>
       <c r="C33">
-        <v>17.87485982147595</v>
+        <v>14.16262795795231</v>
       </c>
       <c r="D33">
-        <v>74.50485982147595</v>
+        <v>72.8626279579523</v>
       </c>
       <c r="E33">
-        <v>-4.629999999999995</v>
+        <v>-2.560000000000002</v>
       </c>
       <c r="F33">
-        <v>64.17</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="G33">
         <v>7.54</v>
@@ -3981,37 +3981,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M33">
-        <v>15.131286</v>
+        <v>15.619392</v>
       </c>
       <c r="N33">
-        <v>-9.887952666666667</v>
+        <v>-10.37605866666667</v>
       </c>
       <c r="O33">
-        <v>-1.878711006666667</v>
+        <v>-1.971451146666666</v>
       </c>
       <c r="P33">
-        <v>-8.009241660000001</v>
+        <v>-8.404607519999999</v>
       </c>
       <c r="Q33">
-        <v>-6.169241660000001</v>
+        <v>-6.564607519999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08958553527395127</v>
+        <v>0.09022944020445056</v>
       </c>
       <c r="T33">
-        <v>0.8019474553872642</v>
+        <v>0.8137408003194299</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.06583930363442561</v>
+        <v>0.06378182539584981</v>
       </c>
       <c r="W33">
-        <v>0.2202750922030025</v>
+        <v>0.2207602455716586</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3465226507075032</v>
+        <v>0.3356938178728938</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1319992979219571</v>
+        <v>0.1338992979219571</v>
       </c>
       <c r="C34">
-        <v>14.16262795795231</v>
+        <v>10.52123072340515</v>
       </c>
       <c r="D34">
-        <v>72.8626279579523</v>
+        <v>71.29123072340515</v>
       </c>
       <c r="E34">
-        <v>-2.560000000000002</v>
+        <v>-0.4899999999999949</v>
       </c>
       <c r="F34">
-        <v>66.23999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="G34">
         <v>7.54</v>
@@ -4063,37 +4063,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M34">
-        <v>15.619392</v>
+        <v>16.107498</v>
       </c>
       <c r="N34">
-        <v>-10.37605866666667</v>
+        <v>-10.86416466666667</v>
       </c>
       <c r="O34">
-        <v>-1.971451146666666</v>
+        <v>-2.064191286666667</v>
       </c>
       <c r="P34">
-        <v>-8.404607519999999</v>
+        <v>-8.799973379999999</v>
       </c>
       <c r="Q34">
-        <v>-6.564607519999999</v>
+        <v>-6.959973379999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09022944020445056</v>
+        <v>0.09089256617765132</v>
       </c>
       <c r="T34">
-        <v>0.8137408003194299</v>
+        <v>0.8258861853988243</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.06378182539584981</v>
+        <v>0.06184904280809679</v>
       </c>
       <c r="W34">
-        <v>0.2207602455716586</v>
+        <v>0.2212159957058508</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3356938178728938</v>
+        <v>0.3255212779373515</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1338992979219571</v>
+        <v>0.1357992979219571</v>
       </c>
       <c r="C35">
-        <v>10.52123072340515</v>
+        <v>6.946181889669489</v>
       </c>
       <c r="D35">
-        <v>71.29123072340515</v>
+        <v>69.78618188966949</v>
       </c>
       <c r="E35">
-        <v>-0.4899999999999949</v>
+        <v>1.580000000000013</v>
       </c>
       <c r="F35">
-        <v>68.31</v>
+        <v>70.38000000000001</v>
       </c>
       <c r="G35">
         <v>7.54</v>
@@ -4145,37 +4145,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M35">
-        <v>16.107498</v>
+        <v>16.595604</v>
       </c>
       <c r="N35">
-        <v>-10.86416466666667</v>
+        <v>-11.35227066666667</v>
       </c>
       <c r="O35">
-        <v>-2.064191286666667</v>
+        <v>-2.156931426666667</v>
       </c>
       <c r="P35">
-        <v>-8.799973379999999</v>
+        <v>-9.195339240000001</v>
       </c>
       <c r="Q35">
-        <v>-6.959973379999999</v>
+        <v>-7.355339240000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09089256617765132</v>
+        <v>0.09157578687731269</v>
       </c>
       <c r="T35">
-        <v>0.8258861853988243</v>
+        <v>0.8383996124503216</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.06184904280809679</v>
+        <v>0.060029953313741</v>
       </c>
       <c r="W35">
-        <v>0.2212159957058508</v>
+        <v>0.2216449370086199</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3255212779373515</v>
+        <v>0.3159471227039</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1357992979219571</v>
+        <v>0.1376992979219571</v>
       </c>
       <c r="C36">
-        <v>6.946181889669489</v>
+        <v>3.433366236137815</v>
       </c>
       <c r="D36">
-        <v>69.78618188966949</v>
+        <v>68.34336623613781</v>
       </c>
       <c r="E36">
-        <v>1.580000000000013</v>
+        <v>3.650000000000006</v>
       </c>
       <c r="F36">
-        <v>70.38000000000001</v>
+        <v>72.45</v>
       </c>
       <c r="G36">
         <v>7.54</v>
@@ -4227,37 +4227,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M36">
-        <v>16.595604</v>
+        <v>17.08371</v>
       </c>
       <c r="N36">
-        <v>-11.35227066666667</v>
+        <v>-11.84037666666667</v>
       </c>
       <c r="O36">
-        <v>-2.156931426666667</v>
+        <v>-2.249671566666667</v>
       </c>
       <c r="P36">
-        <v>-9.195339240000001</v>
+        <v>-9.590705099999999</v>
       </c>
       <c r="Q36">
-        <v>-7.355339240000001</v>
+        <v>-7.750705099999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09157578687731269</v>
+        <v>0.09228002975234828</v>
       </c>
       <c r="T36">
-        <v>0.8383996124503216</v>
+        <v>0.8512980680264803</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.060029953313741</v>
+        <v>0.05831481179049126</v>
       </c>
       <c r="W36">
-        <v>0.2216449370086199</v>
+        <v>0.2220493673798022</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3159471227039</v>
+        <v>0.3069200620552172</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1376992979219571</v>
+        <v>0.1395992979219571</v>
       </c>
       <c r="C37">
-        <v>3.433366236137815</v>
+        <v>-0.02099802591351363</v>
       </c>
       <c r="D37">
-        <v>68.34336623613781</v>
+        <v>66.95900197408649</v>
       </c>
       <c r="E37">
-        <v>3.650000000000006</v>
+        <v>5.720000000000013</v>
       </c>
       <c r="F37">
-        <v>72.45</v>
+        <v>74.52000000000001</v>
       </c>
       <c r="G37">
         <v>7.54</v>
@@ -4309,37 +4309,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M37">
-        <v>17.08371</v>
+        <v>17.571816</v>
       </c>
       <c r="N37">
-        <v>-11.84037666666667</v>
+        <v>-12.32848266666667</v>
       </c>
       <c r="O37">
-        <v>-2.249671566666667</v>
+        <v>-2.342411706666667</v>
       </c>
       <c r="P37">
-        <v>-9.590705099999999</v>
+        <v>-9.986070960000001</v>
       </c>
       <c r="Q37">
-        <v>-7.750705099999999</v>
+        <v>-8.146070960000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09228002975234828</v>
+        <v>0.09300628021722872</v>
       </c>
       <c r="T37">
-        <v>0.8512980680264803</v>
+        <v>0.8645996003393942</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.05831481179049126</v>
+        <v>0.05669495590742206</v>
       </c>
       <c r="W37">
-        <v>0.2220493673798022</v>
+        <v>0.2224313293970299</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3069200620552172</v>
+        <v>0.2983945047759056</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1395992979219571</v>
+        <v>0.1414992979219571</v>
       </c>
       <c r="C38">
-        <v>-0.02099802591349942</v>
+        <v>-3.420392352865775</v>
       </c>
       <c r="D38">
-        <v>66.95900197408649</v>
+        <v>65.62960764713422</v>
       </c>
       <c r="E38">
-        <v>5.719999999999999</v>
+        <v>7.790000000000006</v>
       </c>
       <c r="F38">
-        <v>74.52</v>
+        <v>76.59</v>
       </c>
       <c r="G38">
         <v>7.54</v>
@@ -4391,37 +4391,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M38">
-        <v>17.571816</v>
+        <v>18.059922</v>
       </c>
       <c r="N38">
-        <v>-12.32848266666666</v>
+        <v>-12.81658866666667</v>
       </c>
       <c r="O38">
-        <v>-2.342411706666666</v>
+        <v>-2.435151846666666</v>
       </c>
       <c r="P38">
-        <v>-9.986070959999997</v>
+        <v>-10.38143682</v>
       </c>
       <c r="Q38">
-        <v>-8.146070959999998</v>
+        <v>-8.541436819999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0930062802172287</v>
+        <v>0.09375558625242282</v>
       </c>
       <c r="T38">
-        <v>0.8645996003393941</v>
+        <v>0.8783234035193844</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.05669495590742207</v>
+        <v>0.05516265980181605</v>
       </c>
       <c r="W38">
-        <v>0.2224313293970299</v>
+        <v>0.2227926448187318</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2983945047759056</v>
+        <v>0.2903297884306109</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1414992979219571</v>
+        <v>0.1433992979219572</v>
       </c>
       <c r="C39">
-        <v>-3.420392352865775</v>
+        <v>-6.768027102136884</v>
       </c>
       <c r="D39">
-        <v>65.62960764713422</v>
+        <v>64.35197289786311</v>
       </c>
       <c r="E39">
-        <v>7.790000000000006</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="F39">
-        <v>76.59</v>
+        <v>78.66</v>
       </c>
       <c r="G39">
         <v>7.54</v>
@@ -4473,37 +4473,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M39">
-        <v>18.059922</v>
+        <v>18.548028</v>
       </c>
       <c r="N39">
-        <v>-12.81658866666667</v>
+        <v>-13.30469466666666</v>
       </c>
       <c r="O39">
-        <v>-2.435151846666666</v>
+        <v>-2.527891986666666</v>
       </c>
       <c r="P39">
-        <v>-10.38143682</v>
+        <v>-10.77680268</v>
       </c>
       <c r="Q39">
-        <v>-8.541436819999999</v>
+        <v>-8.936802679999998</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09375558625242282</v>
+        <v>0.09452906345004254</v>
       </c>
       <c r="T39">
-        <v>0.8783234035193844</v>
+        <v>0.8924899100277616</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.05516265980181605</v>
+        <v>0.053711010859663</v>
       </c>
       <c r="W39">
-        <v>0.2227926448187318</v>
+        <v>0.2231349436392915</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2903297884306109</v>
+        <v>0.2826895308403317</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1433992979219572</v>
+        <v>0.1452992979219571</v>
       </c>
       <c r="C40">
-        <v>-6.768027102136884</v>
+        <v>-10.06686741618454</v>
       </c>
       <c r="D40">
-        <v>64.35197289786311</v>
+        <v>63.12313258381546</v>
       </c>
       <c r="E40">
-        <v>9.859999999999999</v>
+        <v>11.93000000000001</v>
       </c>
       <c r="F40">
-        <v>78.66</v>
+        <v>80.73</v>
       </c>
       <c r="G40">
         <v>7.54</v>
@@ -4555,37 +4555,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M40">
-        <v>18.548028</v>
+        <v>19.036134</v>
       </c>
       <c r="N40">
-        <v>-13.30469466666666</v>
+        <v>-13.79280066666667</v>
       </c>
       <c r="O40">
-        <v>-2.527891986666666</v>
+        <v>-2.620632126666667</v>
       </c>
       <c r="P40">
-        <v>-10.77680268</v>
+        <v>-11.17216854</v>
       </c>
       <c r="Q40">
-        <v>-8.936802679999998</v>
+        <v>-9.33216854</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09452906345004254</v>
+        <v>0.09532790055578094</v>
       </c>
       <c r="T40">
-        <v>0.8924899100277616</v>
+        <v>0.9071208921593644</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.053711010859663</v>
+        <v>0.05233380545300498</v>
       </c>
       <c r="W40">
-        <v>0.2231349436392915</v>
+        <v>0.2234596886741814</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2826895308403317</v>
+        <v>0.2754410813316052</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1452992979219571</v>
+        <v>0.1471992979219572</v>
       </c>
       <c r="C41">
-        <v>-10.06686741618454</v>
+        <v>-13.31965619645361</v>
       </c>
       <c r="D41">
-        <v>63.12313258381546</v>
+        <v>61.9403438035464</v>
       </c>
       <c r="E41">
-        <v>11.93000000000001</v>
+        <v>14.00000000000001</v>
       </c>
       <c r="F41">
-        <v>80.73</v>
+        <v>82.80000000000001</v>
       </c>
       <c r="G41">
         <v>7.54</v>
@@ -4637,37 +4637,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M41">
-        <v>19.036134</v>
+        <v>19.52424</v>
       </c>
       <c r="N41">
-        <v>-13.79280066666667</v>
+        <v>-14.28090666666667</v>
       </c>
       <c r="O41">
-        <v>-2.620632126666667</v>
+        <v>-2.713372266666667</v>
       </c>
       <c r="P41">
-        <v>-11.17216854</v>
+        <v>-11.5675344</v>
       </c>
       <c r="Q41">
-        <v>-9.33216854</v>
+        <v>-9.727534400000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09532790055578094</v>
+        <v>0.09615336556504397</v>
       </c>
       <c r="T41">
-        <v>0.9071208921593644</v>
+        <v>0.9222395736953538</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.05233380545300498</v>
+        <v>0.05102546031667985</v>
       </c>
       <c r="W41">
-        <v>0.2234596886741814</v>
+        <v>0.2237681964573269</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2754410813316052</v>
+        <v>0.2685550542983149</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1471992979219572</v>
+        <v>0.1490992979219571</v>
       </c>
       <c r="C42">
-        <v>-13.31965619645361</v>
+        <v>-16.52893454194295</v>
       </c>
       <c r="D42">
-        <v>61.9403438035464</v>
+        <v>60.80106545805706</v>
       </c>
       <c r="E42">
-        <v>14.00000000000001</v>
+        <v>16.07000000000001</v>
       </c>
       <c r="F42">
-        <v>82.80000000000001</v>
+        <v>84.87</v>
       </c>
       <c r="G42">
         <v>7.54</v>
@@ -4719,37 +4719,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M42">
-        <v>19.52424</v>
+        <v>20.012346</v>
       </c>
       <c r="N42">
-        <v>-14.28090666666667</v>
+        <v>-14.76901266666667</v>
       </c>
       <c r="O42">
-        <v>-2.713372266666667</v>
+        <v>-2.806112406666667</v>
       </c>
       <c r="P42">
-        <v>-11.5675344</v>
+        <v>-11.96290026</v>
       </c>
       <c r="Q42">
-        <v>-9.727534400000001</v>
+        <v>-10.12290026</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09615336556504397</v>
+        <v>0.09700681243902776</v>
       </c>
       <c r="T42">
-        <v>0.9222395736953538</v>
+        <v>0.9378707529105292</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.05102546031667985</v>
+        <v>0.04978093689432181</v>
       </c>
       <c r="W42">
-        <v>0.2237681964573269</v>
+        <v>0.2240616550803189</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2685550542983149</v>
+        <v>0.2620049310227464</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1490992979219571</v>
+        <v>0.1509992979219571</v>
       </c>
       <c r="C43">
-        <v>-16.52893454194295</v>
+        <v>-19.69705997293211</v>
       </c>
       <c r="D43">
-        <v>60.80106545805706</v>
+        <v>59.7029400270679</v>
       </c>
       <c r="E43">
-        <v>16.07000000000001</v>
+        <v>18.14000000000001</v>
       </c>
       <c r="F43">
-        <v>84.87</v>
+        <v>86.94000000000001</v>
       </c>
       <c r="G43">
         <v>7.54</v>
@@ -4801,37 +4801,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M43">
-        <v>20.012346</v>
+        <v>20.500452</v>
       </c>
       <c r="N43">
-        <v>-14.76901266666667</v>
+        <v>-15.25711866666667</v>
       </c>
       <c r="O43">
-        <v>-2.806112406666667</v>
+        <v>-2.898852546666667</v>
       </c>
       <c r="P43">
-        <v>-11.96290026</v>
+        <v>-12.35826612</v>
       </c>
       <c r="Q43">
-        <v>-10.12290026</v>
+        <v>-10.51826612</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09700681243902776</v>
+        <v>0.09788968851556271</v>
       </c>
       <c r="T43">
-        <v>0.9378707529105292</v>
+        <v>0.9540409383055383</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.04978093689432181</v>
+        <v>0.04859567649207604</v>
       </c>
       <c r="W43">
-        <v>0.2240616550803189</v>
+        <v>0.2243411394831685</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2620049310227464</v>
+        <v>0.2557667183793476</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1509992979219571</v>
+        <v>0.1528992979219571</v>
       </c>
       <c r="C44">
-        <v>-19.6970599729321</v>
+        <v>-22.82622271491469</v>
       </c>
       <c r="D44">
-        <v>59.7029400270679</v>
+        <v>58.64377728508531</v>
       </c>
       <c r="E44">
-        <v>18.14</v>
+        <v>20.21000000000001</v>
       </c>
       <c r="F44">
-        <v>86.94</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="G44">
         <v>7.54</v>
@@ -4883,37 +4883,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M44">
-        <v>20.500452</v>
+        <v>20.988558</v>
       </c>
       <c r="N44">
-        <v>-15.25711866666667</v>
+        <v>-15.74522466666667</v>
       </c>
       <c r="O44">
-        <v>-2.898852546666666</v>
+        <v>-2.991592686666667</v>
       </c>
       <c r="P44">
-        <v>-12.35826612</v>
+        <v>-12.75363198</v>
       </c>
       <c r="Q44">
-        <v>-10.51826612</v>
+        <v>-10.91363198</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09788968851556271</v>
+        <v>0.09880354270004627</v>
       </c>
       <c r="T44">
-        <v>0.9540409383055383</v>
+        <v>0.970778498626688</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.04859567649207606</v>
+        <v>0.04746554448063242</v>
       </c>
       <c r="W44">
-        <v>0.2243411394831685</v>
+        <v>0.2246076246114669</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2557667183793476</v>
+        <v>0.2498186551612233</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1528992979219571</v>
+        <v>0.1547992979219572</v>
       </c>
       <c r="C45">
-        <v>-22.82622271491469</v>
+        <v>-25.91846027943038</v>
       </c>
       <c r="D45">
-        <v>58.64377728508531</v>
+        <v>57.62153972056961</v>
       </c>
       <c r="E45">
-        <v>20.21000000000001</v>
+        <v>22.28</v>
       </c>
       <c r="F45">
-        <v>89.01000000000001</v>
+        <v>91.08</v>
       </c>
       <c r="G45">
         <v>7.54</v>
@@ -4965,37 +4965,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M45">
-        <v>20.988558</v>
+        <v>21.476664</v>
       </c>
       <c r="N45">
-        <v>-15.74522466666667</v>
+        <v>-16.23333066666667</v>
       </c>
       <c r="O45">
-        <v>-2.991592686666667</v>
+        <v>-3.084332826666667</v>
       </c>
       <c r="P45">
-        <v>-12.75363198</v>
+        <v>-13.14899784</v>
       </c>
       <c r="Q45">
-        <v>-10.91363198</v>
+        <v>-11.30899784</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09880354270004627</v>
+        <v>0.09975003453397567</v>
       </c>
       <c r="T45">
-        <v>0.970778498626688</v>
+        <v>0.9881138289593075</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.04746554448063242</v>
+        <v>0.0463867821060726</v>
       </c>
       <c r="W45">
-        <v>0.2246076246114669</v>
+        <v>0.2248619967793881</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2498186551612233</v>
+        <v>0.2441409584530135</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1547992979219572</v>
+        <v>0.1566992979219571</v>
       </c>
       <c r="C46">
-        <v>-25.91846027943038</v>
+        <v>-28.97567054604657</v>
       </c>
       <c r="D46">
-        <v>57.62153972056961</v>
+        <v>56.63432945395343</v>
       </c>
       <c r="E46">
-        <v>22.28</v>
+        <v>24.35000000000001</v>
       </c>
       <c r="F46">
-        <v>91.08</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="G46">
         <v>7.54</v>
@@ -5047,37 +5047,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M46">
-        <v>21.476664</v>
+        <v>21.96477</v>
       </c>
       <c r="N46">
-        <v>-16.23333066666667</v>
+        <v>-16.72143666666667</v>
       </c>
       <c r="O46">
-        <v>-3.084332826666667</v>
+        <v>-3.177072966666667</v>
       </c>
       <c r="P46">
-        <v>-13.14899784</v>
+        <v>-13.5443637</v>
       </c>
       <c r="Q46">
-        <v>-11.30899784</v>
+        <v>-11.7043637</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09975003453397567</v>
+        <v>0.1007309442527752</v>
       </c>
       <c r="T46">
-        <v>0.9881138289593075</v>
+        <v>1.006079534940386</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.0463867821060726</v>
+        <v>0.04535596472593765</v>
       </c>
       <c r="W46">
-        <v>0.2248619967793881</v>
+        <v>0.2251050635176239</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2441409584530135</v>
+        <v>0.2387156038207243</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1566992979219571</v>
+        <v>0.1585992979219571</v>
       </c>
       <c r="C47">
-        <v>-28.97567054604657</v>
+        <v>-31.99962352221634</v>
       </c>
       <c r="D47">
-        <v>56.63432945395343</v>
+        <v>55.68037647778366</v>
       </c>
       <c r="E47">
-        <v>24.35000000000001</v>
+        <v>26.42</v>
       </c>
       <c r="F47">
-        <v>93.15000000000001</v>
+        <v>95.22</v>
       </c>
       <c r="G47">
         <v>7.54</v>
@@ -5129,37 +5129,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M47">
-        <v>21.96477</v>
+        <v>22.452876</v>
       </c>
       <c r="N47">
-        <v>-16.72143666666667</v>
+        <v>-17.20954266666666</v>
       </c>
       <c r="O47">
-        <v>-3.177072966666667</v>
+        <v>-3.269813106666666</v>
       </c>
       <c r="P47">
-        <v>-13.5443637</v>
+        <v>-13.93972956</v>
       </c>
       <c r="Q47">
-        <v>-11.7043637</v>
+        <v>-12.09972956</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1007309442527752</v>
+        <v>0.10174818396116</v>
       </c>
       <c r="T47">
-        <v>1.006079534940386</v>
+        <v>1.024710637439282</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.04535596472593765</v>
+        <v>0.0443699654927651</v>
       </c>
       <c r="W47">
-        <v>0.2251050635176239</v>
+        <v>0.225337562136806</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2387156038207243</v>
+        <v>0.2335261341724479</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1585992979219571</v>
+        <v>0.1604992979219572</v>
       </c>
       <c r="C48">
-        <v>-31.99962352221634</v>
+        <v>-34.9919719343206</v>
       </c>
       <c r="D48">
-        <v>55.68037647778366</v>
+        <v>54.75802806567941</v>
       </c>
       <c r="E48">
-        <v>26.42</v>
+        <v>28.49000000000001</v>
       </c>
       <c r="F48">
-        <v>95.22</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="G48">
         <v>7.54</v>
@@ -5211,37 +5211,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M48">
-        <v>22.452876</v>
+        <v>22.940982</v>
       </c>
       <c r="N48">
-        <v>-17.20954266666666</v>
+        <v>-17.69764866666667</v>
       </c>
       <c r="O48">
-        <v>-3.269813106666666</v>
+        <v>-3.362553246666667</v>
       </c>
       <c r="P48">
-        <v>-13.93972956</v>
+        <v>-14.33509542</v>
       </c>
       <c r="Q48">
-        <v>-12.09972956</v>
+        <v>-12.49509542</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.10174818396116</v>
+        <v>0.1028038100736347</v>
       </c>
       <c r="T48">
-        <v>1.024710637439282</v>
+        <v>1.044044800409834</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.0443699654927651</v>
+        <v>0.04342592367377009</v>
       </c>
       <c r="W48">
-        <v>0.225337562136806</v>
+        <v>0.225560167197725</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2335261341724479</v>
+        <v>0.2285574930198426</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1604992979219572</v>
+        <v>0.1623992979219571</v>
       </c>
       <c r="C49">
-        <v>-34.9919719343206</v>
+        <v>-37.95426078321595</v>
       </c>
       <c r="D49">
-        <v>54.75802806567941</v>
+        <v>53.86573921678406</v>
       </c>
       <c r="E49">
-        <v>28.49000000000001</v>
+        <v>30.56000000000002</v>
       </c>
       <c r="F49">
-        <v>97.29000000000001</v>
+        <v>99.36000000000001</v>
       </c>
       <c r="G49">
         <v>7.54</v>
@@ -5293,37 +5293,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M49">
-        <v>22.940982</v>
+        <v>23.429088</v>
       </c>
       <c r="N49">
-        <v>-17.69764866666667</v>
+        <v>-18.18575466666667</v>
       </c>
       <c r="O49">
-        <v>-3.362553246666667</v>
+        <v>-3.455293386666667</v>
       </c>
       <c r="P49">
-        <v>-14.33509542</v>
+        <v>-14.73046128</v>
       </c>
       <c r="Q49">
-        <v>-12.49509542</v>
+        <v>-12.89046128</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1028038100736347</v>
+        <v>0.1039000371904353</v>
       </c>
       <c r="T49">
-        <v>1.044044800409834</v>
+        <v>1.0641225850331</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.04342592367377009</v>
+        <v>0.04252121693056654</v>
       </c>
       <c r="W49">
-        <v>0.225560167197725</v>
+        <v>0.2257734970477724</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2285574930198426</v>
+        <v>0.2237958785819292</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1623992979219571</v>
+        <v>0.1642992979219571</v>
       </c>
       <c r="C50">
-        <v>-37.95426078321594</v>
+        <v>-40.88793598050947</v>
       </c>
       <c r="D50">
-        <v>53.86573921678406</v>
+        <v>53.00206401949053</v>
       </c>
       <c r="E50">
-        <v>30.56</v>
+        <v>32.63</v>
       </c>
       <c r="F50">
-        <v>99.36</v>
+        <v>101.43</v>
       </c>
       <c r="G50">
         <v>7.54</v>
@@ -5375,37 +5375,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M50">
-        <v>23.429088</v>
+        <v>23.917194</v>
       </c>
       <c r="N50">
-        <v>-18.18575466666667</v>
+        <v>-18.67386066666666</v>
       </c>
       <c r="O50">
-        <v>-3.455293386666667</v>
+        <v>-3.548033526666666</v>
       </c>
       <c r="P50">
-        <v>-14.73046128</v>
+        <v>-15.12582714</v>
       </c>
       <c r="Q50">
-        <v>-12.89046128</v>
+        <v>-13.28582714</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1039000371904353</v>
+        <v>0.1050392536059341</v>
       </c>
       <c r="T50">
-        <v>1.0641225850331</v>
+        <v>1.08498773375924</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.04252121693056654</v>
+        <v>0.04165343699320805</v>
       </c>
       <c r="W50">
-        <v>0.2257734970477724</v>
+        <v>0.2259781195570016</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2237958785819291</v>
+        <v>0.2192286157537267</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1642992979219571</v>
+        <v>0.1661992979219571</v>
       </c>
       <c r="C51">
-        <v>-40.88793598050947</v>
+        <v>-43.79435216710807</v>
       </c>
       <c r="D51">
-        <v>53.00206401949053</v>
+        <v>52.16564783289193</v>
       </c>
       <c r="E51">
-        <v>32.63</v>
+        <v>34.7</v>
       </c>
       <c r="F51">
-        <v>101.43</v>
+        <v>103.5</v>
       </c>
       <c r="G51">
         <v>7.54</v>
@@ -5457,37 +5457,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M51">
-        <v>23.917194</v>
+        <v>24.4053</v>
       </c>
       <c r="N51">
-        <v>-18.67386066666666</v>
+        <v>-19.16196666666666</v>
       </c>
       <c r="O51">
-        <v>-3.548033526666666</v>
+        <v>-3.640773666666666</v>
       </c>
       <c r="P51">
-        <v>-15.12582714</v>
+        <v>-15.521193</v>
       </c>
       <c r="Q51">
-        <v>-13.28582714</v>
+        <v>-13.681193</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1050392536059341</v>
+        <v>0.1062240386780527</v>
       </c>
       <c r="T51">
-        <v>1.08498773375924</v>
+        <v>1.106687488434424</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.04165343699320805</v>
+        <v>0.04082036825334388</v>
       </c>
       <c r="W51">
-        <v>0.2259781195570016</v>
+        <v>0.2261745571658615</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2192286157537267</v>
+        <v>0.214844043438652</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1661992979219571</v>
+        <v>0.1680992979219571</v>
       </c>
       <c r="C52">
-        <v>-43.79435216710807</v>
+        <v>-46.67477980297023</v>
       </c>
       <c r="D52">
-        <v>52.16564783289193</v>
+        <v>51.35522019702978</v>
       </c>
       <c r="E52">
-        <v>34.7</v>
+        <v>36.77000000000001</v>
       </c>
       <c r="F52">
-        <v>103.5</v>
+        <v>105.57</v>
       </c>
       <c r="G52">
         <v>7.54</v>
@@ -5539,37 +5539,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M52">
-        <v>24.4053</v>
+        <v>24.893406</v>
       </c>
       <c r="N52">
-        <v>-19.16196666666666</v>
+        <v>-19.65007266666667</v>
       </c>
       <c r="O52">
-        <v>-3.640773666666666</v>
+        <v>-3.733513806666667</v>
       </c>
       <c r="P52">
-        <v>-15.521193</v>
+        <v>-15.91655886</v>
       </c>
       <c r="Q52">
-        <v>-13.681193</v>
+        <v>-14.07655886</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1062240386780527</v>
+        <v>0.1074571823245436</v>
       </c>
       <c r="T52">
-        <v>1.106687488434424</v>
+        <v>1.129272947382066</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.04082036825334388</v>
+        <v>0.04001996887582734</v>
       </c>
       <c r="W52">
-        <v>0.2261745571658615</v>
+        <v>0.2263632913390799</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.214844043438652</v>
+        <v>0.2106314151359334</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1680992979219571</v>
+        <v>0.1699992979219571</v>
       </c>
       <c r="C53">
-        <v>-46.67477980297023</v>
+        <v>-49.53041160610384</v>
       </c>
       <c r="D53">
-        <v>51.35522019702978</v>
+        <v>50.56958839389616</v>
       </c>
       <c r="E53">
-        <v>36.77000000000001</v>
+        <v>38.84</v>
       </c>
       <c r="F53">
-        <v>105.57</v>
+        <v>107.64</v>
       </c>
       <c r="G53">
         <v>7.54</v>
@@ -5621,37 +5621,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M53">
-        <v>24.893406</v>
+        <v>25.381512</v>
       </c>
       <c r="N53">
-        <v>-19.65007266666667</v>
+        <v>-20.13817866666667</v>
       </c>
       <c r="O53">
-        <v>-3.733513806666667</v>
+        <v>-3.826253946666667</v>
       </c>
       <c r="P53">
-        <v>-15.91655886</v>
+        <v>-16.31192472</v>
       </c>
       <c r="Q53">
-        <v>-14.07655886</v>
+        <v>-14.47192472</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1074571823245436</v>
+        <v>0.1087417069563049</v>
       </c>
       <c r="T53">
-        <v>1.129272947382066</v>
+        <v>1.152799467119192</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.04001996887582734</v>
+        <v>0.03925035408975373</v>
       </c>
       <c r="W53">
-        <v>0.2263632913390799</v>
+        <v>0.2265447665056361</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2106314151359334</v>
+        <v>0.2065808109987037</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1699992979219571</v>
+        <v>0.1718992979219572</v>
       </c>
       <c r="C54">
-        <v>-49.53041160610384</v>
+        <v>-52.36236840944681</v>
       </c>
       <c r="D54">
-        <v>50.56958839389616</v>
+        <v>49.8076315905532</v>
       </c>
       <c r="E54">
-        <v>38.84</v>
+        <v>40.91000000000001</v>
       </c>
       <c r="F54">
-        <v>107.64</v>
+        <v>109.71</v>
       </c>
       <c r="G54">
         <v>7.54</v>
@@ -5703,37 +5703,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M54">
-        <v>25.381512</v>
+        <v>25.869618</v>
       </c>
       <c r="N54">
-        <v>-20.13817866666667</v>
+        <v>-20.62628466666667</v>
       </c>
       <c r="O54">
-        <v>-3.826253946666667</v>
+        <v>-3.918994086666667</v>
       </c>
       <c r="P54">
-        <v>-16.31192472</v>
+        <v>-16.70729058</v>
       </c>
       <c r="Q54">
-        <v>-14.47192472</v>
+        <v>-14.86729058</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1087417069563049</v>
+        <v>0.1100808922106944</v>
       </c>
       <c r="T54">
-        <v>1.152799467119192</v>
+        <v>1.177327115355771</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03925035408975373</v>
+        <v>0.03850978137107913</v>
       </c>
       <c r="W54">
-        <v>0.2265447665056361</v>
+        <v>0.2267193935526996</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2065808109987037</v>
+        <v>0.2026830598477848</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1718992979219572</v>
+        <v>0.1737992979219571</v>
       </c>
       <c r="C55">
-        <v>-52.36236840944681</v>
+        <v>-55.17170449611618</v>
       </c>
       <c r="D55">
-        <v>49.8076315905532</v>
+        <v>49.06829550388382</v>
       </c>
       <c r="E55">
-        <v>40.91000000000001</v>
+        <v>42.98</v>
       </c>
       <c r="F55">
-        <v>109.71</v>
+        <v>111.78</v>
       </c>
       <c r="G55">
         <v>7.54</v>
@@ -5785,37 +5785,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M55">
-        <v>25.869618</v>
+        <v>26.357724</v>
       </c>
       <c r="N55">
-        <v>-20.62628466666667</v>
+        <v>-21.11439066666667</v>
       </c>
       <c r="O55">
-        <v>-3.918994086666667</v>
+        <v>-4.011734226666666</v>
       </c>
       <c r="P55">
-        <v>-16.70729058</v>
+        <v>-17.10265644</v>
       </c>
       <c r="Q55">
-        <v>-14.86729058</v>
+        <v>-15.26265644</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1100808922106944</v>
+        <v>0.1114783029109269</v>
       </c>
       <c r="T55">
-        <v>1.177327115355771</v>
+        <v>1.202921183080896</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03850978137107913</v>
+        <v>0.0377966372716147</v>
       </c>
       <c r="W55">
-        <v>0.2267193935526996</v>
+        <v>0.2268875529313532</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2026830598477848</v>
+        <v>0.1989296698506038</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1737992979219571</v>
+        <v>0.1756992979219572</v>
       </c>
       <c r="C56">
-        <v>-55.17170449611618</v>
+        <v>-57.9594124664348</v>
       </c>
       <c r="D56">
-        <v>49.06829550388382</v>
+        <v>48.35058753356521</v>
       </c>
       <c r="E56">
-        <v>42.98</v>
+        <v>45.05000000000001</v>
       </c>
       <c r="F56">
-        <v>111.78</v>
+        <v>113.85</v>
       </c>
       <c r="G56">
         <v>7.54</v>
@@ -5867,37 +5867,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M56">
-        <v>26.357724</v>
+        <v>26.84583</v>
       </c>
       <c r="N56">
-        <v>-21.11439066666667</v>
+        <v>-21.60249666666667</v>
       </c>
       <c r="O56">
-        <v>-4.011734226666666</v>
+        <v>-4.104474366666667</v>
       </c>
       <c r="P56">
-        <v>-17.10265644</v>
+        <v>-17.4980223</v>
       </c>
       <c r="Q56">
-        <v>-15.26265644</v>
+        <v>-15.6580223</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1114783029109269</v>
+        <v>0.112937820753392</v>
       </c>
       <c r="T56">
-        <v>1.202921183080896</v>
+        <v>1.229652764927139</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.0377966372716147</v>
+        <v>0.03710942568485807</v>
       </c>
       <c r="W56">
-        <v>0.2268875529313532</v>
+        <v>0.2270495974235105</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1989296698506038</v>
+        <v>0.1953127667624109</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1756992979219572</v>
+        <v>0.1775992979219571</v>
       </c>
       <c r="C57">
-        <v>-57.9594124664348</v>
+        <v>-60.72642768398303</v>
       </c>
       <c r="D57">
-        <v>48.35058753356521</v>
+        <v>47.65357231601699</v>
       </c>
       <c r="E57">
-        <v>45.05000000000001</v>
+        <v>47.12000000000002</v>
       </c>
       <c r="F57">
-        <v>113.85</v>
+        <v>115.92</v>
       </c>
       <c r="G57">
         <v>7.54</v>
@@ -5949,37 +5949,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M57">
-        <v>26.84583</v>
+        <v>27.333936</v>
       </c>
       <c r="N57">
-        <v>-21.60249666666667</v>
+        <v>-22.09060266666667</v>
       </c>
       <c r="O57">
-        <v>-4.104474366666667</v>
+        <v>-4.197214506666668</v>
       </c>
       <c r="P57">
-        <v>-17.4980223</v>
+        <v>-17.89338816</v>
       </c>
       <c r="Q57">
-        <v>-15.6580223</v>
+        <v>-16.05338816</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.112937820753392</v>
+        <v>0.114463680315969</v>
       </c>
       <c r="T57">
-        <v>1.229652764927139</v>
+        <v>1.257599418675482</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03710942568485807</v>
+        <v>0.03644675736905703</v>
       </c>
       <c r="W57">
-        <v>0.2270495974235105</v>
+        <v>0.2272058546123764</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1953127667624109</v>
+        <v>0.1918250387845107</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1775992979219571</v>
+        <v>0.1794992979219572</v>
       </c>
       <c r="C58">
-        <v>-60.72642768398303</v>
+        <v>-63.4736323425541</v>
       </c>
       <c r="D58">
-        <v>47.65357231601699</v>
+        <v>46.97636765744591</v>
       </c>
       <c r="E58">
-        <v>47.12000000000002</v>
+        <v>49.19000000000001</v>
       </c>
       <c r="F58">
-        <v>115.92</v>
+        <v>117.99</v>
       </c>
       <c r="G58">
         <v>7.54</v>
@@ -6031,37 +6031,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M58">
-        <v>27.333936</v>
+        <v>27.822042</v>
       </c>
       <c r="N58">
-        <v>-22.09060266666667</v>
+        <v>-22.57870866666667</v>
       </c>
       <c r="O58">
-        <v>-4.197214506666668</v>
+        <v>-4.289954646666668</v>
       </c>
       <c r="P58">
-        <v>-17.89338816</v>
+        <v>-18.28875402</v>
       </c>
       <c r="Q58">
-        <v>-16.05338816</v>
+        <v>-16.44875402</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.114463680315969</v>
+        <v>0.116060510090759</v>
       </c>
       <c r="T58">
-        <v>1.257599418675482</v>
+        <v>1.286845916784215</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03644675736905703</v>
+        <v>0.03580734057310866</v>
       </c>
       <c r="W58">
-        <v>0.2272058546123764</v>
+        <v>0.227356629092861</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1918250387845107</v>
+        <v>0.1884596872268877</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1794992979219572</v>
+        <v>0.1813992979219571</v>
       </c>
       <c r="C59">
-        <v>-63.4736323425541</v>
+        <v>-66.20185919119544</v>
       </c>
       <c r="D59">
-        <v>46.97636765744591</v>
+        <v>46.31814080880459</v>
       </c>
       <c r="E59">
-        <v>49.19000000000001</v>
+        <v>51.26000000000002</v>
       </c>
       <c r="F59">
-        <v>117.99</v>
+        <v>120.06</v>
       </c>
       <c r="G59">
         <v>7.54</v>
@@ -6113,37 +6113,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M59">
-        <v>27.822042</v>
+        <v>28.31014800000001</v>
       </c>
       <c r="N59">
-        <v>-22.57870866666667</v>
+        <v>-23.06681466666667</v>
       </c>
       <c r="O59">
-        <v>-4.289954646666668</v>
+        <v>-4.382694786666668</v>
       </c>
       <c r="P59">
-        <v>-18.28875402</v>
+        <v>-18.68411988</v>
       </c>
       <c r="Q59">
-        <v>-16.44875402</v>
+        <v>-16.84411988</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.116060510090759</v>
+        <v>0.1177333793786342</v>
       </c>
       <c r="T59">
-        <v>1.286845916784215</v>
+        <v>1.317485105279077</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03580734057310866</v>
+        <v>0.035189972632193</v>
       </c>
       <c r="W59">
-        <v>0.227356629092861</v>
+        <v>0.2275022044533289</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1884596872268877</v>
+        <v>0.1852103822746999</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1813992979219571</v>
+        <v>0.1832992979219571</v>
       </c>
       <c r="C60">
-        <v>-66.20185919119541</v>
+        <v>-68.91189495040837</v>
       </c>
       <c r="D60">
-        <v>46.31814080880459</v>
+        <v>45.67810504959164</v>
       </c>
       <c r="E60">
-        <v>51.25999999999999</v>
+        <v>53.33</v>
       </c>
       <c r="F60">
-        <v>120.06</v>
+        <v>122.13</v>
       </c>
       <c r="G60">
         <v>7.54</v>
@@ -6195,37 +6195,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M60">
-        <v>28.310148</v>
+        <v>28.798254</v>
       </c>
       <c r="N60">
-        <v>-23.06681466666667</v>
+        <v>-23.55492066666667</v>
       </c>
       <c r="O60">
-        <v>-4.382694786666667</v>
+        <v>-4.475434926666667</v>
       </c>
       <c r="P60">
-        <v>-18.68411988</v>
+        <v>-19.07948574</v>
       </c>
       <c r="Q60">
-        <v>-16.84411988</v>
+        <v>-17.23948574</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1177333793786342</v>
+        <v>0.1194878520464058</v>
       </c>
       <c r="T60">
-        <v>1.317485105279077</v>
+        <v>1.349618888334664</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03518997263219301</v>
+        <v>0.03459353241808804</v>
       </c>
       <c r="W60">
-        <v>0.2275022044533289</v>
+        <v>0.2276428450558148</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1852103822747</v>
+        <v>0.1820712232530949</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1832992979219571</v>
+        <v>0.1851992979219571</v>
       </c>
       <c r="C61">
-        <v>-68.91189495040837</v>
+        <v>-71.60448344897321</v>
       </c>
       <c r="D61">
-        <v>45.67810504959164</v>
+        <v>45.05551655102678</v>
       </c>
       <c r="E61">
-        <v>53.33</v>
+        <v>55.39999999999999</v>
       </c>
       <c r="F61">
-        <v>122.13</v>
+        <v>124.2</v>
       </c>
       <c r="G61">
         <v>7.54</v>
@@ -6277,37 +6277,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M61">
-        <v>28.798254</v>
+        <v>29.28636</v>
       </c>
       <c r="N61">
-        <v>-23.55492066666667</v>
+        <v>-24.04302666666666</v>
       </c>
       <c r="O61">
-        <v>-4.475434926666667</v>
+        <v>-4.568175066666666</v>
       </c>
       <c r="P61">
-        <v>-19.07948574</v>
+        <v>-19.4748516</v>
       </c>
       <c r="Q61">
-        <v>-17.23948574</v>
+        <v>-17.6348516</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1194878520464058</v>
+        <v>0.1213300483475659</v>
       </c>
       <c r="T61">
-        <v>1.349618888334664</v>
+        <v>1.383359360543031</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03459353241808804</v>
+        <v>0.03401697354445324</v>
       </c>
       <c r="W61">
-        <v>0.2276428450558148</v>
+        <v>0.227778797638218</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1820712232530949</v>
+        <v>0.1790367028655434</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1851992979219571</v>
+        <v>0.1870992979219571</v>
       </c>
       <c r="C62">
-        <v>-71.60448344897321</v>
+        <v>-74.28032850769551</v>
       </c>
       <c r="D62">
-        <v>45.05551655102678</v>
+        <v>44.44967149230447</v>
       </c>
       <c r="E62">
-        <v>55.39999999999999</v>
+        <v>57.47</v>
       </c>
       <c r="F62">
-        <v>124.2</v>
+        <v>126.27</v>
       </c>
       <c r="G62">
         <v>7.54</v>
@@ -6359,37 +6359,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M62">
-        <v>29.28636</v>
+        <v>29.774466</v>
       </c>
       <c r="N62">
-        <v>-24.04302666666666</v>
+        <v>-24.53113266666666</v>
       </c>
       <c r="O62">
-        <v>-4.568175066666666</v>
+        <v>-4.660915206666666</v>
       </c>
       <c r="P62">
-        <v>-19.4748516</v>
+        <v>-19.87021746</v>
       </c>
       <c r="Q62">
-        <v>-17.6348516</v>
+        <v>-18.03021746</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1213300483475659</v>
+        <v>0.1232667162539138</v>
       </c>
       <c r="T62">
-        <v>1.383359360543031</v>
+        <v>1.418830113377467</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03401697354445324</v>
+        <v>0.0334593182404458</v>
       </c>
       <c r="W62">
-        <v>0.227778797638218</v>
+        <v>0.2279102927589029</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1790367028655434</v>
+        <v>0.1761016749497148</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1870992979219571</v>
+        <v>0.1889992979219571</v>
       </c>
       <c r="C63">
-        <v>-74.28032850769551</v>
+        <v>-76.94009659357963</v>
       </c>
       <c r="D63">
-        <v>44.44967149230447</v>
+        <v>43.85990340642039</v>
       </c>
       <c r="E63">
-        <v>57.47</v>
+        <v>59.54000000000001</v>
       </c>
       <c r="F63">
-        <v>126.27</v>
+        <v>128.34</v>
       </c>
       <c r="G63">
         <v>7.54</v>
@@ -6441,37 +6441,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M63">
-        <v>29.774466</v>
+        <v>30.262572</v>
       </c>
       <c r="N63">
-        <v>-24.53113266666666</v>
+        <v>-25.01923866666667</v>
       </c>
       <c r="O63">
-        <v>-4.660915206666666</v>
+        <v>-4.753655346666667</v>
       </c>
       <c r="P63">
-        <v>-19.87021746</v>
+        <v>-20.26558332</v>
       </c>
       <c r="Q63">
-        <v>-18.03021746</v>
+        <v>-18.42558332</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1232667162539138</v>
+        <v>0.1253053140500694</v>
       </c>
       <c r="T63">
-        <v>1.418830113377467</v>
+        <v>1.456167747940032</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.0334593182404458</v>
+        <v>0.03291965181721281</v>
       </c>
       <c r="W63">
-        <v>0.2279102927589029</v>
+        <v>0.2280375461015012</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1761016749497148</v>
+        <v>0.1732613253537517</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1889992979219571</v>
+        <v>0.1908992979219571</v>
       </c>
       <c r="C64">
-        <v>-76.94009659357963</v>
+        <v>-79.58441926547167</v>
       </c>
       <c r="D64">
-        <v>43.85990340642039</v>
+        <v>43.28558073452833</v>
       </c>
       <c r="E64">
-        <v>59.54000000000001</v>
+        <v>61.61</v>
       </c>
       <c r="F64">
-        <v>128.34</v>
+        <v>130.41</v>
       </c>
       <c r="G64">
         <v>7.54</v>
@@ -6523,37 +6523,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M64">
-        <v>30.262572</v>
+        <v>30.750678</v>
       </c>
       <c r="N64">
-        <v>-25.01923866666667</v>
+        <v>-25.50734466666667</v>
       </c>
       <c r="O64">
-        <v>-4.753655346666667</v>
+        <v>-4.846395486666667</v>
       </c>
       <c r="P64">
-        <v>-20.26558332</v>
+        <v>-20.66094918</v>
       </c>
       <c r="Q64">
-        <v>-18.42558332</v>
+        <v>-18.82094918</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1253053140500694</v>
+        <v>0.1274541063216929</v>
       </c>
       <c r="T64">
-        <v>1.456167747940032</v>
+        <v>1.495523633019493</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03291965181721281</v>
+        <v>0.03239711766138403</v>
       </c>
       <c r="W64">
-        <v>0.2280375461015012</v>
+        <v>0.2281607596554457</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1732613253537517</v>
+        <v>0.1705111455862317</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1908992979219571</v>
+        <v>0.1927992979219571</v>
       </c>
       <c r="C65">
-        <v>-79.58441926547167</v>
+        <v>-82.21389543003993</v>
       </c>
       <c r="D65">
-        <v>43.28558073452833</v>
+        <v>42.72610456996006</v>
       </c>
       <c r="E65">
-        <v>61.61</v>
+        <v>63.67999999999999</v>
       </c>
       <c r="F65">
-        <v>130.41</v>
+        <v>132.48</v>
       </c>
       <c r="G65">
         <v>7.54</v>
@@ -6605,37 +6605,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M65">
-        <v>30.750678</v>
+        <v>31.238784</v>
       </c>
       <c r="N65">
-        <v>-25.50734466666667</v>
+        <v>-25.99545066666666</v>
       </c>
       <c r="O65">
-        <v>-4.846395486666667</v>
+        <v>-4.939135626666666</v>
       </c>
       <c r="P65">
-        <v>-20.66094918</v>
+        <v>-21.05631504</v>
       </c>
       <c r="Q65">
-        <v>-18.82094918</v>
+        <v>-19.21631504</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1274541063216929</v>
+        <v>0.1297222759417399</v>
       </c>
       <c r="T65">
-        <v>1.495523633019493</v>
+        <v>1.537065956158923</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03239711766138403</v>
+        <v>0.03189091269792491</v>
       </c>
       <c r="W65">
-        <v>0.2281607596554457</v>
+        <v>0.2282801227858293</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1705111455862317</v>
+        <v>0.1678469089364469</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1927992979219571</v>
+        <v>0.1946992979219571</v>
       </c>
       <c r="C66">
-        <v>-82.21389543003993</v>
+        <v>-84.82909342503301</v>
       </c>
       <c r="D66">
-        <v>42.72610456996006</v>
+        <v>42.180906574967</v>
       </c>
       <c r="E66">
-        <v>63.67999999999999</v>
+        <v>65.75000000000001</v>
       </c>
       <c r="F66">
-        <v>132.48</v>
+        <v>134.55</v>
       </c>
       <c r="G66">
         <v>7.54</v>
@@ -6687,37 +6687,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M66">
-        <v>31.238784</v>
+        <v>31.72689</v>
       </c>
       <c r="N66">
-        <v>-25.99545066666666</v>
+        <v>-26.48355666666667</v>
       </c>
       <c r="O66">
-        <v>-4.939135626666666</v>
+        <v>-5.031875766666667</v>
       </c>
       <c r="P66">
-        <v>-21.05631504</v>
+        <v>-21.45168090000001</v>
       </c>
       <c r="Q66">
-        <v>-19.21631504</v>
+        <v>-19.61168090000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1297222759417399</v>
+        <v>0.1321200552543611</v>
       </c>
       <c r="T66">
-        <v>1.537065956158923</v>
+        <v>1.580982126334892</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03189091269792491</v>
+        <v>0.03140028327180298</v>
       </c>
       <c r="W66">
-        <v>0.2282801227858293</v>
+        <v>0.2283958132045089</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1678469089364469</v>
+        <v>0.165264648798963</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1946992979219571</v>
+        <v>0.1965992979219571</v>
       </c>
       <c r="C67">
-        <v>-84.82909342503301</v>
+        <v>-87.43055294504954</v>
       </c>
       <c r="D67">
-        <v>42.180906574967</v>
+        <v>41.64944705495046</v>
       </c>
       <c r="E67">
-        <v>65.75000000000001</v>
+        <v>67.82000000000001</v>
       </c>
       <c r="F67">
-        <v>134.55</v>
+        <v>136.62</v>
       </c>
       <c r="G67">
         <v>7.54</v>
@@ -6769,37 +6769,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M67">
-        <v>31.72689</v>
+        <v>32.214996</v>
       </c>
       <c r="N67">
-        <v>-26.48355666666667</v>
+        <v>-26.97166266666667</v>
       </c>
       <c r="O67">
-        <v>-5.031875766666667</v>
+        <v>-5.124615906666667</v>
       </c>
       <c r="P67">
-        <v>-21.45168090000001</v>
+        <v>-21.84704676</v>
       </c>
       <c r="Q67">
-        <v>-19.61168090000001</v>
+        <v>-20.00704676</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1321200552543611</v>
+        <v>0.1346588804089011</v>
       </c>
       <c r="T67">
-        <v>1.580982126334892</v>
+        <v>1.62748160063886</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03140028327180298</v>
+        <v>0.0309245214040484</v>
       </c>
       <c r="W67">
-        <v>0.2283958132045089</v>
+        <v>0.2285079978529254</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.165264648798963</v>
+        <v>0.1627606389686758</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1965992979219571</v>
+        <v>0.1984992979219571</v>
       </c>
       <c r="C68">
-        <v>-87.43055294504954</v>
+        <v>-90.018786823537</v>
       </c>
       <c r="D68">
-        <v>41.64944705495046</v>
+        <v>41.13121317646301</v>
       </c>
       <c r="E68">
-        <v>67.82000000000001</v>
+        <v>69.89</v>
       </c>
       <c r="F68">
-        <v>136.62</v>
+        <v>138.69</v>
       </c>
       <c r="G68">
         <v>7.54</v>
@@ -6851,37 +6851,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M68">
-        <v>32.214996</v>
+        <v>32.703102</v>
       </c>
       <c r="N68">
-        <v>-26.97166266666667</v>
+        <v>-27.45976866666667</v>
       </c>
       <c r="O68">
-        <v>-5.124615906666667</v>
+        <v>-5.217356046666668</v>
       </c>
       <c r="P68">
-        <v>-21.84704676</v>
+        <v>-22.24241262</v>
       </c>
       <c r="Q68">
-        <v>-20.00704676</v>
+        <v>-20.40241262</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1346588804089011</v>
+        <v>0.1373515737546254</v>
       </c>
       <c r="T68">
-        <v>1.62748160063886</v>
+        <v>1.676799224900643</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0309245214040484</v>
+        <v>0.03046296138309245</v>
       </c>
       <c r="W68">
-        <v>0.2285079978529254</v>
+        <v>0.2286168337058668</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1627606389686758</v>
+        <v>0.1603313757004865</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1984992979219571</v>
+        <v>0.2003992979219572</v>
       </c>
       <c r="C69">
-        <v>-90.018786823537</v>
+        <v>-92.59428268338712</v>
       </c>
       <c r="D69">
-        <v>41.13121317646301</v>
+        <v>40.62571731661291</v>
       </c>
       <c r="E69">
-        <v>69.89</v>
+        <v>71.96000000000002</v>
       </c>
       <c r="F69">
-        <v>138.69</v>
+        <v>140.76</v>
       </c>
       <c r="G69">
         <v>7.54</v>
@@ -6933,37 +6933,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M69">
-        <v>32.703102</v>
+        <v>33.191208</v>
       </c>
       <c r="N69">
-        <v>-27.45976866666667</v>
+        <v>-27.94787466666667</v>
       </c>
       <c r="O69">
-        <v>-5.217356046666668</v>
+        <v>-5.310096186666668</v>
       </c>
       <c r="P69">
-        <v>-22.24241262</v>
+        <v>-22.63777848</v>
       </c>
       <c r="Q69">
-        <v>-20.40241262</v>
+        <v>-20.79777848</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1373515737546254</v>
+        <v>0.1402125604344574</v>
       </c>
       <c r="T69">
-        <v>1.676799224900643</v>
+        <v>1.729199200678788</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03046296138309245</v>
+        <v>0.0300149766568705</v>
       </c>
       <c r="W69">
-        <v>0.2286168337058668</v>
+        <v>0.2287224685043099</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1603313757004865</v>
+        <v>0.15797356135195</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2003992979219572</v>
+        <v>0.2022992979219572</v>
       </c>
       <c r="C70">
-        <v>-92.59428268338712</v>
+        <v>-95.15750446729606</v>
       </c>
       <c r="D70">
-        <v>40.62571731661291</v>
+        <v>40.13249553270394</v>
       </c>
       <c r="E70">
-        <v>71.96000000000002</v>
+        <v>74.03000000000002</v>
       </c>
       <c r="F70">
-        <v>140.76</v>
+        <v>142.83</v>
       </c>
       <c r="G70">
         <v>7.54</v>
@@ -7015,37 +7015,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M70">
-        <v>33.191208</v>
+        <v>33.67931400000001</v>
       </c>
       <c r="N70">
-        <v>-27.94787466666667</v>
+        <v>-28.43598066666667</v>
       </c>
       <c r="O70">
-        <v>-5.310096186666668</v>
+        <v>-5.402836326666668</v>
       </c>
       <c r="P70">
-        <v>-22.63777848</v>
+        <v>-23.03314434000001</v>
       </c>
       <c r="Q70">
-        <v>-20.79777848</v>
+        <v>-21.19314434000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1402125604344574</v>
+        <v>0.1432581269000851</v>
       </c>
       <c r="T70">
-        <v>1.729199200678788</v>
+        <v>1.784979820055524</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0300149766568705</v>
+        <v>0.02957997699517672</v>
       </c>
       <c r="W70">
-        <v>0.2287224685043099</v>
+        <v>0.2288250414245374</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.15797356135195</v>
+        <v>0.1556840894482985</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2022992979219572</v>
+        <v>0.2041992979219572</v>
       </c>
       <c r="C71">
-        <v>-95.15750446729606</v>
+        <v>-97.70889385798452</v>
       </c>
       <c r="D71">
-        <v>40.13249553270394</v>
+        <v>39.65110614201548</v>
       </c>
       <c r="E71">
-        <v>74.03000000000002</v>
+        <v>76.10000000000001</v>
       </c>
       <c r="F71">
-        <v>142.83</v>
+        <v>144.9</v>
       </c>
       <c r="G71">
         <v>7.54</v>
@@ -7097,37 +7097,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M71">
-        <v>33.67931400000001</v>
+        <v>34.16742</v>
       </c>
       <c r="N71">
-        <v>-28.43598066666667</v>
+        <v>-28.92408666666667</v>
       </c>
       <c r="O71">
-        <v>-5.402836326666668</v>
+        <v>-5.495576466666667</v>
       </c>
       <c r="P71">
-        <v>-23.03314434000001</v>
+        <v>-23.4285102</v>
       </c>
       <c r="Q71">
-        <v>-21.19314434000001</v>
+        <v>-21.5885102</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1432581269000851</v>
+        <v>0.1465067311300879</v>
       </c>
       <c r="T71">
-        <v>1.784979820055524</v>
+        <v>1.844479147390708</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02957997699517672</v>
+        <v>0.02915740589524563</v>
       </c>
       <c r="W71">
-        <v>0.2288250414245374</v>
+        <v>0.2289246836899011</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1556840894482985</v>
+        <v>0.1534600310276085</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2041992979219572</v>
+        <v>0.2060992979219571</v>
       </c>
       <c r="C72">
-        <v>-97.70889385798452</v>
+        <v>-100.2488715974162</v>
       </c>
       <c r="D72">
-        <v>39.65110614201548</v>
+        <v>39.18112840258388</v>
       </c>
       <c r="E72">
-        <v>76.10000000000001</v>
+        <v>78.17000000000003</v>
       </c>
       <c r="F72">
-        <v>144.9</v>
+        <v>146.97</v>
       </c>
       <c r="G72">
         <v>7.54</v>
@@ -7179,37 +7179,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M72">
-        <v>34.16742</v>
+        <v>34.65552600000001</v>
       </c>
       <c r="N72">
-        <v>-28.92408666666667</v>
+        <v>-29.41219266666668</v>
       </c>
       <c r="O72">
-        <v>-5.495576466666667</v>
+        <v>-5.588316606666669</v>
       </c>
       <c r="P72">
-        <v>-23.4285102</v>
+        <v>-23.82387606000001</v>
       </c>
       <c r="Q72">
-        <v>-21.5885102</v>
+        <v>-21.98387606000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1465067311300879</v>
+        <v>0.1499793770311255</v>
       </c>
       <c r="T72">
-        <v>1.844479147390708</v>
+        <v>1.908081876611077</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02915740589524563</v>
+        <v>0.02874673820658019</v>
       </c>
       <c r="W72">
-        <v>0.2289246836899011</v>
+        <v>0.2290215191308884</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1534600310276085</v>
+        <v>0.1512986221398956</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2060992979219571</v>
+        <v>0.2079992979219571</v>
       </c>
       <c r="C73">
-        <v>-100.2488715974161</v>
+        <v>-102.7778387132955</v>
       </c>
       <c r="D73">
-        <v>39.18112840258388</v>
+        <v>38.72216128670448</v>
       </c>
       <c r="E73">
-        <v>78.17</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="F73">
-        <v>146.97</v>
+        <v>149.04</v>
       </c>
       <c r="G73">
         <v>7.54</v>
@@ -7261,37 +7261,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M73">
-        <v>34.655526</v>
+        <v>35.143632</v>
       </c>
       <c r="N73">
-        <v>-29.41219266666667</v>
+        <v>-29.90029866666666</v>
       </c>
       <c r="O73">
-        <v>-5.588316606666667</v>
+        <v>-5.681056746666666</v>
       </c>
       <c r="P73">
-        <v>-23.82387606</v>
+        <v>-24.21924192</v>
       </c>
       <c r="Q73">
-        <v>-21.98387606</v>
+        <v>-22.37924192</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1499793770311254</v>
+        <v>0.1537000690679513</v>
       </c>
       <c r="T73">
-        <v>1.908081876611076</v>
+        <v>1.976227657918615</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0287467382065802</v>
+        <v>0.02834747795371103</v>
       </c>
       <c r="W73">
-        <v>0.2290215191308884</v>
+        <v>0.2291156646985149</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1512986221398958</v>
+        <v>0.1491972523879528</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2079992979219571</v>
+        <v>0.2098992979219571</v>
       </c>
       <c r="C74">
-        <v>-102.7778387132955</v>
+        <v>-105.2961776603624</v>
       </c>
       <c r="D74">
-        <v>38.72216128670448</v>
+        <v>38.27382233963763</v>
       </c>
       <c r="E74">
-        <v>80.23999999999999</v>
+        <v>82.30999999999999</v>
       </c>
       <c r="F74">
-        <v>149.04</v>
+        <v>151.11</v>
       </c>
       <c r="G74">
         <v>7.54</v>
@@ -7343,37 +7343,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M74">
-        <v>35.143632</v>
+        <v>35.631738</v>
       </c>
       <c r="N74">
-        <v>-29.90029866666666</v>
+        <v>-30.38840466666667</v>
       </c>
       <c r="O74">
-        <v>-5.681056746666666</v>
+        <v>-5.773796886666666</v>
       </c>
       <c r="P74">
-        <v>-24.21924192</v>
+        <v>-24.61460778</v>
       </c>
       <c r="Q74">
-        <v>-22.37924192</v>
+        <v>-22.77460778</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1537000690679513</v>
+        <v>0.1576963679223199</v>
       </c>
       <c r="T74">
-        <v>1.976227657918615</v>
+        <v>2.049421274878564</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02834747795371103</v>
+        <v>0.02795915633790677</v>
       </c>
       <c r="W74">
-        <v>0.2291156646985149</v>
+        <v>0.2292072309355216</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1491972523879528</v>
+        <v>0.1471534544100356</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2098992979219571</v>
+        <v>0.2117992979219571</v>
       </c>
       <c r="C75">
-        <v>-105.2961776603624</v>
+        <v>-107.8042533833061</v>
       </c>
       <c r="D75">
-        <v>38.27382233963763</v>
+        <v>37.83574661669392</v>
       </c>
       <c r="E75">
-        <v>82.30999999999999</v>
+        <v>84.38000000000001</v>
       </c>
       <c r="F75">
-        <v>151.11</v>
+        <v>153.18</v>
       </c>
       <c r="G75">
         <v>7.54</v>
@@ -7425,37 +7425,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M75">
-        <v>35.631738</v>
+        <v>36.119844</v>
       </c>
       <c r="N75">
-        <v>-30.38840466666667</v>
+        <v>-30.87651066666667</v>
       </c>
       <c r="O75">
-        <v>-5.773796886666666</v>
+        <v>-5.866537026666667</v>
       </c>
       <c r="P75">
-        <v>-24.61460778</v>
+        <v>-25.00997364</v>
       </c>
       <c r="Q75">
-        <v>-22.77460778</v>
+        <v>-23.16997364</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1576963679223199</v>
+        <v>0.1620000743808707</v>
       </c>
       <c r="T75">
-        <v>2.049421274878564</v>
+        <v>2.128245170066201</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02795915633790677</v>
+        <v>0.02758132990090803</v>
       </c>
       <c r="W75">
-        <v>0.2292072309355216</v>
+        <v>0.2292963224093659</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1471534544100356</v>
+        <v>0.1451648942153053</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2117992979219571</v>
+        <v>0.2136992979219571</v>
       </c>
       <c r="C76">
-        <v>-107.8042533833061</v>
+        <v>-110.3024143075116</v>
       </c>
       <c r="D76">
-        <v>37.83574661669392</v>
+        <v>37.4075856924884</v>
       </c>
       <c r="E76">
-        <v>84.38000000000001</v>
+        <v>86.45</v>
       </c>
       <c r="F76">
-        <v>153.18</v>
+        <v>155.25</v>
       </c>
       <c r="G76">
         <v>7.54</v>
@@ -7507,37 +7507,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M76">
-        <v>36.119844</v>
+        <v>36.60795</v>
       </c>
       <c r="N76">
-        <v>-30.87651066666667</v>
+        <v>-31.36461666666667</v>
       </c>
       <c r="O76">
-        <v>-5.866537026666667</v>
+        <v>-5.959277166666667</v>
       </c>
       <c r="P76">
-        <v>-25.00997364</v>
+        <v>-25.4053395</v>
       </c>
       <c r="Q76">
-        <v>-23.16997364</v>
+        <v>-23.5653395</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1620000743808707</v>
+        <v>0.1666480773561055</v>
       </c>
       <c r="T76">
-        <v>2.128245170066201</v>
+        <v>2.213374976868849</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02758132990090803</v>
+        <v>0.02721357883556259</v>
       </c>
       <c r="W76">
-        <v>0.2292963224093659</v>
+        <v>0.2293830381105743</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1451648942153053</v>
+        <v>0.1432293622924347</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2136992979219571</v>
+        <v>0.2155992979219571</v>
       </c>
       <c r="C77">
-        <v>-110.3024143075116</v>
+        <v>-112.7909932632879</v>
       </c>
       <c r="D77">
-        <v>37.4075856924884</v>
+        <v>36.98900673671206</v>
       </c>
       <c r="E77">
-        <v>86.45</v>
+        <v>88.52</v>
       </c>
       <c r="F77">
-        <v>155.25</v>
+        <v>157.32</v>
       </c>
       <c r="G77">
         <v>7.54</v>
@@ -7589,37 +7589,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M77">
-        <v>36.60795</v>
+        <v>37.096056</v>
       </c>
       <c r="N77">
-        <v>-31.36461666666667</v>
+        <v>-31.85272266666666</v>
       </c>
       <c r="O77">
-        <v>-5.959277166666667</v>
+        <v>-6.052017306666666</v>
       </c>
       <c r="P77">
-        <v>-25.4053395</v>
+        <v>-25.80070536</v>
       </c>
       <c r="Q77">
-        <v>-23.5653395</v>
+        <v>-23.96070536</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1666480773561055</v>
+        <v>0.1716834139126099</v>
       </c>
       <c r="T77">
-        <v>2.213374976868849</v>
+        <v>2.305598934238384</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02721357883556259</v>
+        <v>0.0268555054298315</v>
       </c>
       <c r="W77">
-        <v>0.2293830381105743</v>
+        <v>0.2294674718196457</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1432293622924347</v>
+        <v>0.1413447654201657</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2155992979219571</v>
+        <v>0.2174992979219572</v>
       </c>
       <c r="C78">
-        <v>-112.7909932632879</v>
+        <v>-115.2703083487328</v>
       </c>
       <c r="D78">
-        <v>36.98900673671206</v>
+        <v>36.57969165126717</v>
       </c>
       <c r="E78">
-        <v>88.52</v>
+        <v>90.59000000000002</v>
       </c>
       <c r="F78">
-        <v>157.32</v>
+        <v>159.39</v>
       </c>
       <c r="G78">
         <v>7.54</v>
@@ -7671,37 +7671,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M78">
-        <v>37.096056</v>
+        <v>37.58416200000001</v>
       </c>
       <c r="N78">
-        <v>-31.85272266666666</v>
+        <v>-32.34082866666667</v>
       </c>
       <c r="O78">
-        <v>-6.052017306666666</v>
+        <v>-6.144757446666668</v>
       </c>
       <c r="P78">
-        <v>-25.80070536</v>
+        <v>-26.19607122000001</v>
       </c>
       <c r="Q78">
-        <v>-23.96070536</v>
+        <v>-24.35607122000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1716834139126099</v>
+        <v>0.1771566058218538</v>
       </c>
       <c r="T78">
-        <v>2.305598934238384</v>
+        <v>2.405842366161792</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0268555054298315</v>
+        <v>0.02650673263204148</v>
       </c>
       <c r="W78">
-        <v>0.2294674718196457</v>
+        <v>0.2295497124453646</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1413447654201657</v>
+        <v>0.1395091191160077</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2174992979219572</v>
+        <v>0.2193992979219571</v>
       </c>
       <c r="C79">
-        <v>-115.2703083487328</v>
+        <v>-117.740663735934</v>
       </c>
       <c r="D79">
-        <v>36.57969165126717</v>
+        <v>36.17933626406597</v>
       </c>
       <c r="E79">
-        <v>90.59000000000002</v>
+        <v>92.66000000000001</v>
       </c>
       <c r="F79">
-        <v>159.39</v>
+        <v>161.46</v>
       </c>
       <c r="G79">
         <v>7.54</v>
@@ -7753,37 +7753,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M79">
-        <v>37.58416200000001</v>
+        <v>38.072268</v>
       </c>
       <c r="N79">
-        <v>-32.34082866666667</v>
+        <v>-32.82893466666667</v>
       </c>
       <c r="O79">
-        <v>-6.144757446666668</v>
+        <v>-6.237497586666668</v>
       </c>
       <c r="P79">
-        <v>-26.19607122000001</v>
+        <v>-26.59143708</v>
       </c>
       <c r="Q79">
-        <v>-24.35607122000001</v>
+        <v>-24.75143708</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1771566058218538</v>
+        <v>0.1831273606319381</v>
       </c>
       <c r="T79">
-        <v>2.405842366161792</v>
+        <v>2.515198837350965</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02650673263204148</v>
+        <v>0.02616690272650249</v>
       </c>
       <c r="W79">
-        <v>0.2295497124453646</v>
+        <v>0.2296298443370907</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1395091191160077</v>
+        <v>0.1377205406658025</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2193992979219571</v>
+        <v>0.2212992979219572</v>
       </c>
       <c r="C80">
-        <v>-117.740663735934</v>
+        <v>-120.2023504248022</v>
       </c>
       <c r="D80">
-        <v>36.17933626406597</v>
+        <v>35.78764957519784</v>
       </c>
       <c r="E80">
-        <v>92.66000000000001</v>
+        <v>94.73</v>
       </c>
       <c r="F80">
-        <v>161.46</v>
+        <v>163.53</v>
       </c>
       <c r="G80">
         <v>7.54</v>
@@ -7835,37 +7835,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M80">
-        <v>38.072268</v>
+        <v>38.560374</v>
       </c>
       <c r="N80">
-        <v>-32.82893466666667</v>
+        <v>-33.31704066666667</v>
       </c>
       <c r="O80">
-        <v>-6.237497586666668</v>
+        <v>-6.330237726666668</v>
       </c>
       <c r="P80">
-        <v>-26.59143708</v>
+        <v>-26.98680294</v>
       </c>
       <c r="Q80">
-        <v>-24.75143708</v>
+        <v>-25.14680294</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1831273606319381</v>
+        <v>0.1896667587572685</v>
       </c>
       <c r="T80">
-        <v>2.515198837350965</v>
+        <v>2.634970210558154</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02616690272650249</v>
+        <v>0.02583567610971132</v>
       </c>
       <c r="W80">
-        <v>0.2296298443370907</v>
+        <v>0.2297079475733301</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1377205406658025</v>
+        <v>0.1359772426826911</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2212992979219572</v>
+        <v>0.2231992979219572</v>
       </c>
       <c r="C81">
-        <v>-120.2023504248022</v>
+        <v>-122.6556469484603</v>
       </c>
       <c r="D81">
-        <v>35.78764957519784</v>
+        <v>35.40435305153977</v>
       </c>
       <c r="E81">
-        <v>94.73</v>
+        <v>96.80000000000003</v>
       </c>
       <c r="F81">
-        <v>163.53</v>
+        <v>165.6</v>
       </c>
       <c r="G81">
         <v>7.54</v>
@@ -7917,37 +7917,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M81">
-        <v>38.560374</v>
+        <v>39.04848</v>
       </c>
       <c r="N81">
-        <v>-33.31704066666667</v>
+        <v>-33.80514666666667</v>
       </c>
       <c r="O81">
-        <v>-6.330237726666668</v>
+        <v>-6.422977866666668</v>
       </c>
       <c r="P81">
-        <v>-26.98680294</v>
+        <v>-27.38216880000001</v>
       </c>
       <c r="Q81">
-        <v>-25.14680294</v>
+        <v>-25.54216880000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1896667587572685</v>
+        <v>0.1968600966951319</v>
       </c>
       <c r="T81">
-        <v>2.634970210558154</v>
+        <v>2.766718721086062</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02583567610971132</v>
+        <v>0.02551273015833993</v>
       </c>
       <c r="W81">
-        <v>0.2297079475733301</v>
+        <v>0.2297840982286635</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1359772426826911</v>
+        <v>0.1342775271491574</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2231992979219572</v>
+        <v>0.2250992979219572</v>
       </c>
       <c r="C82">
-        <v>-122.6556469484603</v>
+        <v>-125.1008200337849</v>
       </c>
       <c r="D82">
-        <v>35.40435305153977</v>
+        <v>35.02917996621509</v>
       </c>
       <c r="E82">
-        <v>96.80000000000003</v>
+        <v>98.87000000000002</v>
       </c>
       <c r="F82">
-        <v>165.6</v>
+        <v>167.67</v>
       </c>
       <c r="G82">
         <v>7.54</v>
@@ -7999,37 +7999,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M82">
-        <v>39.04848</v>
+        <v>39.53658600000001</v>
       </c>
       <c r="N82">
-        <v>-33.80514666666667</v>
+        <v>-34.29325266666667</v>
       </c>
       <c r="O82">
-        <v>-6.422977866666668</v>
+        <v>-6.515718006666669</v>
       </c>
       <c r="P82">
-        <v>-27.38216880000001</v>
+        <v>-27.77753466000001</v>
       </c>
       <c r="Q82">
-        <v>-25.54216880000001</v>
+        <v>-25.93753466000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1968600966951319</v>
+        <v>0.2048106281001389</v>
       </c>
       <c r="T82">
-        <v>2.766718721086062</v>
+        <v>2.912335495880065</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02551273015833993</v>
+        <v>0.02519775818107647</v>
       </c>
       <c r="W82">
-        <v>0.2297840982286635</v>
+        <v>0.2298583686209022</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1342775271491574</v>
+        <v>0.1326197799004024</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2250992979219572</v>
+        <v>0.2269992979219572</v>
       </c>
       <c r="C83">
-        <v>-125.1008200337849</v>
+        <v>-127.5381252203893</v>
       </c>
       <c r="D83">
-        <v>35.02917996621509</v>
+        <v>34.66187477961069</v>
       </c>
       <c r="E83">
-        <v>98.87000000000002</v>
+        <v>100.94</v>
       </c>
       <c r="F83">
-        <v>167.67</v>
+        <v>169.74</v>
       </c>
       <c r="G83">
         <v>7.54</v>
@@ -8081,37 +8081,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M83">
-        <v>39.53658600000001</v>
+        <v>40.024692</v>
       </c>
       <c r="N83">
-        <v>-34.29325266666667</v>
+        <v>-34.78135866666667</v>
       </c>
       <c r="O83">
-        <v>-6.515718006666669</v>
+        <v>-6.608458146666667</v>
       </c>
       <c r="P83">
-        <v>-27.77753466000001</v>
+        <v>-28.17290052</v>
       </c>
       <c r="Q83">
-        <v>-25.93753466000001</v>
+        <v>-26.33290052</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2048106281001389</v>
+        <v>0.2136445518834799</v>
       </c>
       <c r="T83">
-        <v>2.912335495880065</v>
+        <v>3.074131912317847</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02519775818107647</v>
+        <v>0.0248904684471609</v>
       </c>
       <c r="W83">
-        <v>0.2298583686209022</v>
+        <v>0.2299308275401595</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1326197799004024</v>
+        <v>0.1310024655113732</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2269992979219572</v>
+        <v>0.2288992979219572</v>
       </c>
       <c r="C84">
-        <v>-127.5381252203893</v>
+        <v>-129.9678074410679</v>
       </c>
       <c r="D84">
-        <v>34.66187477961069</v>
+        <v>34.30219255893209</v>
       </c>
       <c r="E84">
-        <v>100.94</v>
+        <v>103.01</v>
       </c>
       <c r="F84">
-        <v>169.74</v>
+        <v>171.81</v>
       </c>
       <c r="G84">
         <v>7.54</v>
@@ -8163,37 +8163,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M84">
-        <v>40.024692</v>
+        <v>40.512798</v>
       </c>
       <c r="N84">
-        <v>-34.78135866666667</v>
+        <v>-35.26946466666667</v>
       </c>
       <c r="O84">
-        <v>-6.608458146666667</v>
+        <v>-6.701198286666668</v>
       </c>
       <c r="P84">
-        <v>-28.17290052</v>
+        <v>-28.56826638</v>
       </c>
       <c r="Q84">
-        <v>-26.33290052</v>
+        <v>-26.72826638</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2136445518834799</v>
+        <v>0.2235177608178023</v>
       </c>
       <c r="T84">
-        <v>3.074131912317847</v>
+        <v>3.25496320127772</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0248904684471609</v>
+        <v>0.02459058328514692</v>
       </c>
       <c r="W84">
-        <v>0.2299308275401595</v>
+        <v>0.2300015404613624</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1310024655113732</v>
+        <v>0.1294241225534047</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2288992979219572</v>
+        <v>0.2307992979219572</v>
       </c>
       <c r="C85">
-        <v>-129.9678074410679</v>
+        <v>-132.390101566473</v>
       </c>
       <c r="D85">
-        <v>34.30219255893209</v>
+        <v>33.94989843352704</v>
       </c>
       <c r="E85">
-        <v>103.01</v>
+        <v>105.08</v>
       </c>
       <c r="F85">
-        <v>171.81</v>
+        <v>173.88</v>
       </c>
       <c r="G85">
         <v>7.54</v>
@@ -8245,37 +8245,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M85">
-        <v>40.512798</v>
+        <v>41.00090400000001</v>
       </c>
       <c r="N85">
-        <v>-35.26946466666667</v>
+        <v>-35.75757066666667</v>
       </c>
       <c r="O85">
-        <v>-6.701198286666668</v>
+        <v>-6.793938426666668</v>
       </c>
       <c r="P85">
-        <v>-28.56826638</v>
+        <v>-28.96363224000001</v>
       </c>
       <c r="Q85">
-        <v>-26.72826638</v>
+        <v>-27.12363224000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2235177608178023</v>
+        <v>0.234625120868915</v>
       </c>
       <c r="T85">
-        <v>3.25496320127772</v>
+        <v>3.458398401357578</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02459058328514692</v>
+        <v>0.02429783824603802</v>
       </c>
       <c r="W85">
-        <v>0.2300015404613624</v>
+        <v>0.2300705697415842</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1294241225534047</v>
+        <v>0.1278833591896738</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2307992979219571</v>
+        <v>0.2326992979219571</v>
       </c>
       <c r="C86">
-        <v>-132.390101566473</v>
+        <v>-134.8052329165684</v>
       </c>
       <c r="D86">
-        <v>33.94989843352702</v>
+        <v>33.60476708343158</v>
       </c>
       <c r="E86">
-        <v>105.08</v>
+        <v>107.15</v>
       </c>
       <c r="F86">
-        <v>173.88</v>
+        <v>175.95</v>
       </c>
       <c r="G86">
         <v>7.54</v>
@@ -8327,37 +8327,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M86">
-        <v>41.000904</v>
+        <v>41.48901</v>
       </c>
       <c r="N86">
-        <v>-35.75757066666667</v>
+        <v>-36.24567666666667</v>
       </c>
       <c r="O86">
-        <v>-6.793938426666666</v>
+        <v>-6.886678566666667</v>
       </c>
       <c r="P86">
-        <v>-28.96363224</v>
+        <v>-29.3589981</v>
       </c>
       <c r="Q86">
-        <v>-27.12363224</v>
+        <v>-27.5189981</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2346251208689148</v>
+        <v>0.2472134622601758</v>
       </c>
       <c r="T86">
-        <v>3.458398401357576</v>
+        <v>3.688958294781414</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02429783824603803</v>
+        <v>0.0240119813254964</v>
       </c>
       <c r="W86">
-        <v>0.2300705697415842</v>
+        <v>0.2301379748034479</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1278833591896738</v>
+        <v>0.1263788490815599</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2326992979219571</v>
+        <v>0.2345992979219571</v>
       </c>
       <c r="C87">
-        <v>-134.8052329165684</v>
+        <v>-137.2134177412012</v>
       </c>
       <c r="D87">
-        <v>33.60476708343158</v>
+        <v>33.26658225879885</v>
       </c>
       <c r="E87">
-        <v>107.15</v>
+        <v>109.22</v>
       </c>
       <c r="F87">
-        <v>175.95</v>
+        <v>178.02</v>
       </c>
       <c r="G87">
         <v>7.54</v>
@@ -8409,37 +8409,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M87">
-        <v>41.48901</v>
+        <v>41.977116</v>
       </c>
       <c r="N87">
-        <v>-36.24567666666667</v>
+        <v>-36.73378266666667</v>
       </c>
       <c r="O87">
-        <v>-6.886678566666667</v>
+        <v>-6.979418706666667</v>
       </c>
       <c r="P87">
-        <v>-29.3589981</v>
+        <v>-29.75436396</v>
       </c>
       <c r="Q87">
-        <v>-27.5189981</v>
+        <v>-27.91436396</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2472134622601758</v>
+        <v>0.2616001381359027</v>
       </c>
       <c r="T87">
-        <v>3.688958294781414</v>
+        <v>3.95245531583723</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0240119813254964</v>
+        <v>0.02373277224031621</v>
       </c>
       <c r="W87">
-        <v>0.2301379748034479</v>
+        <v>0.2302038123057334</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1263788490815599</v>
+        <v>0.1249093275806116</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2345992979219571</v>
+        <v>0.2364992979219571</v>
       </c>
       <c r="C88">
-        <v>-137.2134177412012</v>
+        <v>-139.6148636719439</v>
       </c>
       <c r="D88">
-        <v>33.26658225879885</v>
+        <v>32.93513632805616</v>
       </c>
       <c r="E88">
-        <v>109.22</v>
+        <v>111.29</v>
       </c>
       <c r="F88">
-        <v>178.02</v>
+        <v>180.09</v>
       </c>
       <c r="G88">
         <v>7.54</v>
@@ -8491,37 +8491,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M88">
-        <v>41.977116</v>
+        <v>42.465222</v>
       </c>
       <c r="N88">
-        <v>-36.73378266666667</v>
+        <v>-37.22188866666667</v>
       </c>
       <c r="O88">
-        <v>-6.979418706666667</v>
+        <v>-7.072158846666667</v>
       </c>
       <c r="P88">
-        <v>-29.75436396</v>
+        <v>-30.14972982</v>
       </c>
       <c r="Q88">
-        <v>-27.91436396</v>
+        <v>-28.30972982</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2616001381359027</v>
+        <v>0.2782001487617414</v>
       </c>
       <c r="T88">
-        <v>3.95245531583723</v>
+        <v>4.256490340132402</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02373277224031621</v>
+        <v>0.02345998175479534</v>
       </c>
       <c r="W88">
-        <v>0.2302038123057334</v>
+        <v>0.2302681363022193</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1249093275806116</v>
+        <v>0.1234735881831333</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2364992979219571</v>
+        <v>0.2383992979219571</v>
       </c>
       <c r="C89">
-        <v>-139.6148636719439</v>
+        <v>-142.0097701471931</v>
       </c>
       <c r="D89">
-        <v>32.93513632805616</v>
+        <v>32.61022985280687</v>
       </c>
       <c r="E89">
-        <v>111.29</v>
+        <v>113.36</v>
       </c>
       <c r="F89">
-        <v>180.09</v>
+        <v>182.16</v>
       </c>
       <c r="G89">
         <v>7.54</v>
@@ -8573,37 +8573,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M89">
-        <v>42.465222</v>
+        <v>42.953328</v>
       </c>
       <c r="N89">
-        <v>-37.22188866666667</v>
+        <v>-37.70999466666667</v>
       </c>
       <c r="O89">
-        <v>-7.072158846666667</v>
+        <v>-7.164898986666667</v>
       </c>
       <c r="P89">
-        <v>-30.14972982</v>
+        <v>-30.54509568</v>
       </c>
       <c r="Q89">
-        <v>-28.30972982</v>
+        <v>-28.70509568</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2782001487617414</v>
+        <v>0.2975668278252198</v>
       </c>
       <c r="T89">
-        <v>4.256490340132402</v>
+        <v>4.611197868476768</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02345998175479534</v>
+        <v>0.0231933910530363</v>
       </c>
       <c r="W89">
-        <v>0.2302681363022193</v>
+        <v>0.230330998389694</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1234735881831333</v>
+        <v>0.1220704792265068</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2383992979219571</v>
+        <v>0.2402992979219572</v>
       </c>
       <c r="C90">
-        <v>-142.0097701471931</v>
+        <v>-144.3983288123518</v>
       </c>
       <c r="D90">
-        <v>32.61022985280687</v>
+        <v>32.29167118764813</v>
       </c>
       <c r="E90">
-        <v>113.36</v>
+        <v>115.43</v>
       </c>
       <c r="F90">
-        <v>182.16</v>
+        <v>184.23</v>
       </c>
       <c r="G90">
         <v>7.54</v>
@@ -8655,37 +8655,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M90">
-        <v>42.953328</v>
+        <v>43.441434</v>
       </c>
       <c r="N90">
-        <v>-37.70999466666667</v>
+        <v>-38.19810066666667</v>
       </c>
       <c r="O90">
-        <v>-7.164898986666667</v>
+        <v>-7.257639126666668</v>
       </c>
       <c r="P90">
-        <v>-30.54509568</v>
+        <v>-30.94046154</v>
       </c>
       <c r="Q90">
-        <v>-28.70509568</v>
+        <v>-29.10046154</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2975668278252198</v>
+        <v>0.3204547212638762</v>
       </c>
       <c r="T90">
-        <v>4.611197868476768</v>
+        <v>5.03039767470193</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0231933910530363</v>
+        <v>0.02293279115356398</v>
       </c>
       <c r="W90">
-        <v>0.230330998389694</v>
+        <v>0.2303924478459896</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1220704792265068</v>
+        <v>0.1206989008082314</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2402992979219572</v>
+        <v>0.2421992979219572</v>
       </c>
       <c r="C91">
-        <v>-144.3983288123518</v>
+        <v>-146.780723896783</v>
       </c>
       <c r="D91">
-        <v>32.29167118764813</v>
+        <v>31.97927610321705</v>
       </c>
       <c r="E91">
-        <v>115.43</v>
+        <v>117.5</v>
       </c>
       <c r="F91">
-        <v>184.23</v>
+        <v>186.3</v>
       </c>
       <c r="G91">
         <v>7.54</v>
@@ -8737,37 +8737,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M91">
-        <v>43.441434</v>
+        <v>43.92954</v>
       </c>
       <c r="N91">
-        <v>-38.19810066666667</v>
+        <v>-38.68620666666667</v>
       </c>
       <c r="O91">
-        <v>-7.257639126666668</v>
+        <v>-7.350379266666668</v>
       </c>
       <c r="P91">
-        <v>-30.94046154</v>
+        <v>-31.3358274</v>
       </c>
       <c r="Q91">
-        <v>-29.10046154</v>
+        <v>-29.4958274</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3204547212638762</v>
+        <v>0.3479201933902638</v>
       </c>
       <c r="T91">
-        <v>5.03039767470193</v>
+        <v>5.533437442172123</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02293279115356398</v>
+        <v>0.02267798236296882</v>
       </c>
       <c r="W91">
-        <v>0.2303924478459896</v>
+        <v>0.230452531758812</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1206989008082314</v>
+        <v>0.1193578019103622</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2421992979219572</v>
+        <v>0.2440992979219572</v>
       </c>
       <c r="C92">
-        <v>-146.780723896783</v>
+        <v>-149.1571325690921</v>
       </c>
       <c r="D92">
-        <v>31.97927610321705</v>
+        <v>31.67286743090786</v>
       </c>
       <c r="E92">
-        <v>117.5</v>
+        <v>119.57</v>
       </c>
       <c r="F92">
-        <v>186.3</v>
+        <v>188.37</v>
       </c>
       <c r="G92">
         <v>7.54</v>
@@ -8819,37 +8819,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M92">
-        <v>43.92954</v>
+        <v>44.417646</v>
       </c>
       <c r="N92">
-        <v>-38.68620666666667</v>
+        <v>-39.17431266666667</v>
       </c>
       <c r="O92">
-        <v>-7.350379266666668</v>
+        <v>-7.443119406666668</v>
       </c>
       <c r="P92">
-        <v>-31.3358274</v>
+        <v>-31.73119326</v>
       </c>
       <c r="Q92">
-        <v>-29.4958274</v>
+        <v>-29.89119326</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3479201933902638</v>
+        <v>0.3814891037669598</v>
       </c>
       <c r="T92">
-        <v>5.533437442172123</v>
+        <v>6.148263824635693</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02267798236296882</v>
+        <v>0.02242877376557356</v>
       </c>
       <c r="W92">
-        <v>0.230452531758812</v>
+        <v>0.2305112951460778</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1193578019103622</v>
+        <v>0.118046177713545</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2440992979219572</v>
+        <v>0.2459992979219572</v>
       </c>
       <c r="C93">
-        <v>-149.1571325690921</v>
+        <v>-151.5277252721803</v>
       </c>
       <c r="D93">
-        <v>31.67286743090786</v>
+        <v>31.37227472781966</v>
       </c>
       <c r="E93">
-        <v>119.57</v>
+        <v>121.64</v>
       </c>
       <c r="F93">
-        <v>188.37</v>
+        <v>190.44</v>
       </c>
       <c r="G93">
         <v>7.54</v>
@@ -8901,37 +8901,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M93">
-        <v>44.417646</v>
+        <v>44.905752</v>
       </c>
       <c r="N93">
-        <v>-39.17431266666667</v>
+        <v>-39.66241866666667</v>
       </c>
       <c r="O93">
-        <v>-7.443119406666668</v>
+        <v>-7.535859546666667</v>
       </c>
       <c r="P93">
-        <v>-31.73119326</v>
+        <v>-32.12655912</v>
       </c>
       <c r="Q93">
-        <v>-29.89119326</v>
+        <v>-30.28655912</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3814891037669598</v>
+        <v>0.4234502417378299</v>
       </c>
       <c r="T93">
-        <v>6.148263824635693</v>
+        <v>6.916796802715156</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02242877376557356</v>
+        <v>0.02218498274638255</v>
       </c>
       <c r="W93">
-        <v>0.2305112951460778</v>
+        <v>0.230568781068403</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.118046177713545</v>
+        <v>0.1167630670862239</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2459992979219572</v>
+        <v>0.2478992979219572</v>
       </c>
       <c r="C94">
-        <v>-151.5277252721803</v>
+        <v>-153.8926660393961</v>
       </c>
       <c r="D94">
-        <v>31.37227472781966</v>
+        <v>31.07733396060396</v>
       </c>
       <c r="E94">
-        <v>121.64</v>
+        <v>123.71</v>
       </c>
       <c r="F94">
-        <v>190.44</v>
+        <v>192.51</v>
       </c>
       <c r="G94">
         <v>7.54</v>
@@ -8983,37 +8983,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M94">
-        <v>44.905752</v>
+        <v>45.39385800000001</v>
       </c>
       <c r="N94">
-        <v>-39.66241866666667</v>
+        <v>-40.15052466666668</v>
       </c>
       <c r="O94">
-        <v>-7.535859546666667</v>
+        <v>-7.628599686666669</v>
       </c>
       <c r="P94">
-        <v>-32.12655912</v>
+        <v>-32.52192498000001</v>
       </c>
       <c r="Q94">
-        <v>-30.28655912</v>
+        <v>-30.68192498000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4234502417378299</v>
+        <v>0.4774002762718057</v>
       </c>
       <c r="T94">
-        <v>6.916796802715156</v>
+        <v>7.904910631674466</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02218498274638255</v>
+        <v>0.02194643454480854</v>
       </c>
       <c r="W94">
-        <v>0.230568781068403</v>
+        <v>0.2306250307343342</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1167630670862239</v>
+        <v>0.1155075502358344</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2478992979219572</v>
+        <v>0.2497992979219571</v>
       </c>
       <c r="C95">
-        <v>-153.8926660393961</v>
+        <v>-156.2521127930204</v>
       </c>
       <c r="D95">
-        <v>31.07733396060396</v>
+        <v>30.78788720697965</v>
       </c>
       <c r="E95">
-        <v>123.71</v>
+        <v>125.78</v>
       </c>
       <c r="F95">
-        <v>192.51</v>
+        <v>194.58</v>
       </c>
       <c r="G95">
         <v>7.54</v>
@@ -9065,37 +9065,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M95">
-        <v>45.39385800000001</v>
+        <v>45.881964</v>
       </c>
       <c r="N95">
-        <v>-40.15052466666668</v>
+        <v>-40.63863066666667</v>
       </c>
       <c r="O95">
-        <v>-7.628599686666669</v>
+        <v>-7.721339826666668</v>
       </c>
       <c r="P95">
-        <v>-32.52192498000001</v>
+        <v>-32.91729084000001</v>
       </c>
       <c r="Q95">
-        <v>-30.68192498000001</v>
+        <v>-31.07729084000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4774002762718057</v>
+        <v>0.54933365565044</v>
       </c>
       <c r="T95">
-        <v>7.904910631674466</v>
+        <v>9.222395736953546</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02194643454480854</v>
+        <v>0.02171296183688504</v>
       </c>
       <c r="W95">
-        <v>0.2306250307343342</v>
+        <v>0.2306800835988625</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1155075502358344</v>
+        <v>0.1142787465099212</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2497992979219571</v>
+        <v>0.2516992979219572</v>
       </c>
       <c r="C96">
-        <v>-156.2521127930204</v>
+        <v>-158.6062176262259</v>
       </c>
       <c r="D96">
-        <v>30.78788720697965</v>
+        <v>30.50378237377405</v>
       </c>
       <c r="E96">
-        <v>125.78</v>
+        <v>127.85</v>
       </c>
       <c r="F96">
-        <v>194.58</v>
+        <v>196.65</v>
       </c>
       <c r="G96">
         <v>7.54</v>
@@ -9147,37 +9147,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M96">
-        <v>45.881964</v>
+        <v>46.37007000000001</v>
       </c>
       <c r="N96">
-        <v>-40.63863066666667</v>
+        <v>-41.12673666666667</v>
       </c>
       <c r="O96">
-        <v>-7.721339826666668</v>
+        <v>-7.814079966666668</v>
       </c>
       <c r="P96">
-        <v>-32.91729084000001</v>
+        <v>-33.31265670000001</v>
       </c>
       <c r="Q96">
-        <v>-31.07729084000001</v>
+        <v>-31.47265670000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.54933365565044</v>
+        <v>0.6500403867805283</v>
       </c>
       <c r="T96">
-        <v>9.222395736953546</v>
+        <v>11.06687488434426</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02171296183688504</v>
+        <v>0.0214844043438652</v>
       </c>
       <c r="W96">
-        <v>0.2306800835988625</v>
+        <v>0.2307339774557166</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1142787465099212</v>
+        <v>0.1130758123361326</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2516992979219572</v>
+        <v>0.2535992979219571</v>
       </c>
       <c r="C97">
-        <v>-158.6062176262259</v>
+        <v>-160.9551270695675</v>
       </c>
       <c r="D97">
-        <v>30.50378237377405</v>
+        <v>30.22487293043255</v>
       </c>
       <c r="E97">
-        <v>127.85</v>
+        <v>129.92</v>
       </c>
       <c r="F97">
-        <v>196.65</v>
+        <v>198.72</v>
       </c>
       <c r="G97">
         <v>7.54</v>
@@ -9229,37 +9229,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M97">
-        <v>46.37007000000001</v>
+        <v>46.85817600000001</v>
       </c>
       <c r="N97">
-        <v>-41.12673666666667</v>
+        <v>-41.61484266666668</v>
       </c>
       <c r="O97">
-        <v>-7.814079966666668</v>
+        <v>-7.906820106666668</v>
       </c>
       <c r="P97">
-        <v>-33.31265670000001</v>
+        <v>-33.70802256</v>
       </c>
       <c r="Q97">
-        <v>-31.47265670000001</v>
+        <v>-31.86802256</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6500403867805283</v>
+        <v>0.8011004834756608</v>
       </c>
       <c r="T97">
-        <v>11.06687488434426</v>
+        <v>13.83359360543033</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0214844043438652</v>
+        <v>0.02126060846528327</v>
       </c>
       <c r="W97">
-        <v>0.2307339774557166</v>
+        <v>0.2307867485238862</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1130758123361326</v>
+        <v>0.1118979392909646</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2535992979219571</v>
+        <v>0.2554992979219571</v>
       </c>
       <c r="C98">
-        <v>-160.9551270695675</v>
+        <v>-163.2989823429847</v>
       </c>
       <c r="D98">
-        <v>30.22487293043255</v>
+        <v>29.9510176570153</v>
       </c>
       <c r="E98">
-        <v>129.92</v>
+        <v>131.99</v>
       </c>
       <c r="F98">
-        <v>198.72</v>
+        <v>200.79</v>
       </c>
       <c r="G98">
         <v>7.54</v>
@@ -9311,37 +9311,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M98">
-        <v>46.858176</v>
+        <v>47.346282</v>
       </c>
       <c r="N98">
-        <v>-41.61484266666667</v>
+        <v>-42.10294866666667</v>
       </c>
       <c r="O98">
-        <v>-7.906820106666667</v>
+        <v>-7.999560246666667</v>
       </c>
       <c r="P98">
-        <v>-33.70802256</v>
+        <v>-34.10338842</v>
       </c>
       <c r="Q98">
-        <v>-31.86802256</v>
+        <v>-32.26338842</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8011004834756587</v>
+        <v>1.052867311300879</v>
       </c>
       <c r="T98">
-        <v>13.83359360543029</v>
+        <v>18.44479147390706</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02126060846528327</v>
+        <v>0.02104142693471334</v>
       </c>
       <c r="W98">
-        <v>0.2307867485238862</v>
+        <v>0.2308384315287946</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1118979392909646</v>
+        <v>0.1107443522879649</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2554992979219571</v>
+        <v>0.2573992979219571</v>
       </c>
       <c r="C99">
-        <v>-163.2989823429847</v>
+        <v>-165.6379195942289</v>
       </c>
       <c r="D99">
-        <v>29.9510176570153</v>
+        <v>29.68208040577113</v>
       </c>
       <c r="E99">
-        <v>131.99</v>
+        <v>134.06</v>
       </c>
       <c r="F99">
-        <v>200.79</v>
+        <v>202.86</v>
       </c>
       <c r="G99">
         <v>7.54</v>
@@ -9393,37 +9393,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M99">
-        <v>47.346282</v>
+        <v>47.834388</v>
       </c>
       <c r="N99">
-        <v>-42.10294866666667</v>
+        <v>-42.59105466666666</v>
       </c>
       <c r="O99">
-        <v>-7.999560246666667</v>
+        <v>-8.092300386666667</v>
       </c>
       <c r="P99">
-        <v>-34.10338842</v>
+        <v>-34.49875428</v>
       </c>
       <c r="Q99">
-        <v>-32.26338842</v>
+        <v>-32.65875428</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.052867311300879</v>
+        <v>1.556400966951318</v>
       </c>
       <c r="T99">
-        <v>18.44479147390706</v>
+        <v>27.66718721086059</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02104142693471334</v>
+        <v>0.02082671849660402</v>
       </c>
       <c r="W99">
-        <v>0.2308384315287946</v>
+        <v>0.2308890597785008</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1107443522879649</v>
+        <v>0.1096143078768632</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2573992979219571</v>
+        <v>0.2592992979219572</v>
       </c>
       <c r="C100">
-        <v>-165.6379195942289</v>
+        <v>-167.9720701245579</v>
       </c>
       <c r="D100">
-        <v>29.68208040577113</v>
+        <v>29.41792987544207</v>
       </c>
       <c r="E100">
-        <v>134.06</v>
+        <v>136.13</v>
       </c>
       <c r="F100">
-        <v>202.86</v>
+        <v>204.93</v>
       </c>
       <c r="G100">
         <v>7.54</v>
@@ -9475,37 +9475,37 @@
         <v>5.243333333333334</v>
       </c>
       <c r="M100">
-        <v>47.834388</v>
+        <v>48.32249400000001</v>
       </c>
       <c r="N100">
-        <v>-42.59105466666666</v>
+        <v>-43.07916066666667</v>
       </c>
       <c r="O100">
-        <v>-8.092300386666667</v>
+        <v>-8.185040526666668</v>
       </c>
       <c r="P100">
-        <v>-34.49875428</v>
+        <v>-34.89412014000001</v>
       </c>
       <c r="Q100">
-        <v>-32.65875428</v>
+        <v>-33.05412014000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.556400966951318</v>
+        <v>3.067001933902635</v>
       </c>
       <c r="T100">
-        <v>27.66718721086059</v>
+        <v>55.33437442172118</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02082671849660402</v>
+        <v>0.02061634760269893</v>
       </c>
       <c r="W100">
-        <v>0.2308890597785008</v>
+        <v>0.2309386652352836</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1096143078768632</v>
+        <v>0.1085070926457838</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2592992979219572</v>
-      </c>
-      <c r="C101">
-        <v>-167.9720701245579</v>
-      </c>
-      <c r="D101">
-        <v>29.41792987544207</v>
-      </c>
-      <c r="E101">
-        <v>136.13</v>
-      </c>
-      <c r="F101">
-        <v>204.93</v>
-      </c>
-      <c r="G101">
-        <v>7.54</v>
-      </c>
-      <c r="H101">
-        <v>138.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>7.083333333333334</v>
-      </c>
-      <c r="K101">
-        <v>1.84</v>
-      </c>
-      <c r="L101">
-        <v>5.243333333333334</v>
-      </c>
-      <c r="M101">
-        <v>48.32249400000001</v>
-      </c>
-      <c r="N101">
-        <v>-43.07916066666667</v>
-      </c>
-      <c r="O101">
-        <v>-8.185040526666668</v>
-      </c>
-      <c r="P101">
-        <v>-34.89412014000001</v>
-      </c>
-      <c r="Q101">
-        <v>-33.05412014000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.067001933902635</v>
-      </c>
-      <c r="T101">
-        <v>55.33437442172118</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02061634760269893</v>
-      </c>
-      <c r="W101">
-        <v>0.2309386652352836</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1085070926457838</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
